--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ32"/>
+  <dimension ref="A1:AQ26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0645</v>
+        <v>0.0779</v>
       </c>
       <c r="E2">
-        <v>0.0968</v>
+        <v>0.1345</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,91 +600,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>9.425935959462883e-05</v>
+        <v>3.658448912799784e-05</v>
       </c>
       <c r="J2">
-        <v>7.433222939560334e-05</v>
+        <v>2.875102206676257e-05</v>
       </c>
       <c r="K2">
-        <v>325.313</v>
+        <v>325.092</v>
       </c>
       <c r="L2">
-        <v>0.2683781794902256</v>
+        <v>0.3861092272993424</v>
       </c>
       <c r="M2">
-        <v>31.0167</v>
+        <v>16.555</v>
       </c>
       <c r="N2">
-        <v>0.005313790255986788</v>
+        <v>0.008986147599713399</v>
       </c>
       <c r="O2">
-        <v>0.09534417622412876</v>
+        <v>0.05092404611617635</v>
       </c>
       <c r="P2">
-        <v>31.0167</v>
+        <v>16.552</v>
       </c>
       <c r="Q2">
-        <v>0.005313790255986788</v>
+        <v>0.008984519182751808</v>
       </c>
       <c r="R2">
-        <v>0.09534417622412876</v>
+        <v>0.05091481795922385</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.0001812141347025068</v>
       </c>
       <c r="U2">
-        <v>639.596</v>
+        <v>548.355</v>
       </c>
       <c r="V2">
-        <v>0.1095757766805665</v>
+        <v>0.2976501943244241</v>
       </c>
       <c r="W2">
-        <v>0.1038318726417222</v>
+        <v>0.06832479672929395</v>
       </c>
       <c r="X2">
-        <v>0.05168640279578712</v>
+        <v>0.1371146833235211</v>
       </c>
       <c r="Y2">
-        <v>0.05214546984593504</v>
+        <v>-0.06878988659422719</v>
       </c>
       <c r="Z2">
-        <v>0.2802849406057811</v>
+        <v>0.1899382278414376</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06192844022948111</v>
+        <v>0.1473444202270199</v>
       </c>
       <c r="AC2">
-        <v>-0.06192844022948111</v>
+        <v>-0.1473444202270199</v>
       </c>
       <c r="AD2">
-        <v>3167.918</v>
+        <v>2368.402</v>
       </c>
       <c r="AE2">
-        <v>0.2487204141176411</v>
+        <v>0.03098497136694392</v>
       </c>
       <c r="AF2">
-        <v>3168.166720414118</v>
+        <v>2368.432984971367</v>
       </c>
       <c r="AG2">
-        <v>2528.570720414118</v>
+        <v>1820.077984971367</v>
       </c>
       <c r="AH2">
-        <v>0.3518157722629015</v>
+        <v>0.5624778970745907</v>
       </c>
       <c r="AI2">
-        <v>0.5391755356472727</v>
+        <v>0.5174617967035562</v>
       </c>
       <c r="AJ2">
-        <v>0.3022584782021164</v>
+        <v>0.4969688906546356</v>
       </c>
       <c r="AK2">
-        <v>0.4828879606089764</v>
+        <v>0.4517819157862546</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>19316.57317073171</v>
+        <v>64010.86486486487</v>
       </c>
       <c r="AP2">
-        <v>15418.11414886657</v>
+        <v>49191.29689111802</v>
       </c>
     </row>
     <row r="3">
@@ -728,19 +728,19 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>-0.083</v>
+        <v>0.127</v>
       </c>
       <c r="L3">
-        <v>-0.1049304677623262</v>
+        <v>0.1024193548387097</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.003</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.0001492537313432836</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.02362204724409449</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -749,61 +749,64 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.003</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>6.26</v>
+        <v>0.226</v>
       </c>
       <c r="V3">
-        <v>0.1296066252587992</v>
+        <v>0.01124378109452736</v>
       </c>
       <c r="W3">
-        <v>-0.007685185185185185</v>
+        <v>0.01</v>
       </c>
       <c r="X3">
-        <v>0.04043092519893435</v>
+        <v>0.08089407829052034</v>
       </c>
       <c r="Y3">
-        <v>-0.04811611038411953</v>
+        <v>-0.07089407829052034</v>
       </c>
       <c r="Z3">
-        <v>0.1102900167317345</v>
+        <v>0.1893708002443494</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0405231989161093</v>
+        <v>0.08105500042662896</v>
       </c>
       <c r="AC3">
-        <v>-0.0405231989161093</v>
+        <v>-0.08105500042662896</v>
       </c>
       <c r="AD3">
-        <v>0.108</v>
+        <v>0.043</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.108</v>
+        <v>0.043</v>
       </c>
       <c r="AG3">
-        <v>-6.152</v>
+        <v>-0.183</v>
       </c>
       <c r="AH3">
-        <v>0.002231036192364899</v>
+        <v>0.002134736633073524</v>
       </c>
       <c r="AI3">
-        <v>0.008432229856339788</v>
+        <v>0.006028319080330856</v>
       </c>
       <c r="AJ3">
-        <v>-0.1459618487235456</v>
+        <v>-0.009188130742581712</v>
       </c>
       <c r="AK3">
-        <v>-0.9395235186316434</v>
+        <v>-0.0264948602866657</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -820,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Multi Finance PLC (COSE:MFL.N0000)</t>
+          <t>LOLC Development Finance PLC (COSE:NIFL.N0000)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -829,7 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0863</v>
+        <v>0.0723</v>
+      </c>
+      <c r="E4">
+        <v>-0.0701</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -844,10 +850,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>-0.446</v>
+        <v>0.407</v>
       </c>
       <c r="L4">
-        <v>-1.380804953560371</v>
+        <v>0.05537414965986395</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -856,7 +862,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -865,61 +871,61 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.122</v>
+        <v>1.44</v>
       </c>
       <c r="V4">
-        <v>0.02510288065843621</v>
+        <v>0.002856009520031733</v>
       </c>
       <c r="W4">
-        <v>-0.1496644295302013</v>
+        <v>0.02713333333333333</v>
       </c>
       <c r="X4">
-        <v>0.04094158061218758</v>
+        <v>0.08240942547679794</v>
       </c>
       <c r="Y4">
-        <v>-0.1906060101423889</v>
+        <v>-0.05527609214346461</v>
       </c>
       <c r="Z4">
-        <v>0.1096774193548387</v>
+        <v>0.1191441076349489</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04202050366722161</v>
+        <v>0.08589900019535747</v>
       </c>
       <c r="AC4">
-        <v>-0.04202050366722161</v>
+        <v>-0.08589900019535747</v>
       </c>
       <c r="AD4">
-        <v>0.14</v>
+        <v>25</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.14</v>
+        <v>25</v>
       </c>
       <c r="AG4">
-        <v>0.01800000000000002</v>
+        <v>23.56</v>
       </c>
       <c r="AH4">
-        <v>0.028</v>
+        <v>0.04724111866969009</v>
       </c>
       <c r="AI4">
-        <v>0.05714285714285714</v>
+        <v>0.6720430107526881</v>
       </c>
       <c r="AJ4">
-        <v>0.003690036900369007</v>
+        <v>0.0446415037138093</v>
       </c>
       <c r="AK4">
-        <v>0.007731958762886603</v>
+        <v>0.6588366890380313</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -936,7 +942,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SMB Leasing PLC (COSE:SEMB.N0000)</t>
+          <t>Central Finance Company PLC (COSE:CFIN.N0000)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -945,10 +951,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0475</v>
+        <v>0.0294</v>
       </c>
       <c r="E5">
-        <v>-0.234</v>
+        <v>0.113</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -963,82 +969,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0.115</v>
+        <v>22.6</v>
       </c>
       <c r="L5">
-        <v>0.1116504854368932</v>
+        <v>0.5113122171945701</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>2.18</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.05633074935400516</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.09646017699115045</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>2.18</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.05633074935400516</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.09646017699115045</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>11.1</v>
+        <v>2.84</v>
       </c>
       <c r="V5">
-        <v>0.1321428571428571</v>
+        <v>0.07338501291989663</v>
       </c>
       <c r="W5">
-        <v>0.02031802120141343</v>
+        <v>0.08705701078582434</v>
       </c>
       <c r="X5">
-        <v>0.04099426012761656</v>
+        <v>0.08335945733977876</v>
       </c>
       <c r="Y5">
-        <v>-0.02067623892620313</v>
+        <v>0.003697553446045582</v>
       </c>
       <c r="Z5">
-        <v>0.1255638181153237</v>
+        <v>0.1680480571819633</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.042241909965307</v>
+        <v>0.08850645057279349</v>
       </c>
       <c r="AC5">
-        <v>-0.042241909965307</v>
+        <v>-0.08850645057279349</v>
       </c>
       <c r="AD5">
-        <v>2.65</v>
+        <v>3.07</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>2.65</v>
+        <v>3.07</v>
       </c>
       <c r="AG5">
-        <v>-8.449999999999999</v>
+        <v>0.23</v>
       </c>
       <c r="AH5">
-        <v>0.03058280438545874</v>
+        <v>0.07349772564041177</v>
       </c>
       <c r="AI5">
-        <v>0.1413333333333333</v>
+        <v>0.01878020431883526</v>
       </c>
       <c r="AJ5">
-        <v>-0.1118464592984778</v>
+        <v>0.005908040071923966</v>
       </c>
       <c r="AK5">
-        <v>-1.104575163398692</v>
+        <v>0.001431862043204881</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1055,7 +1064,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Central Finance Company PLC (COSE:CFIN.N0000)</t>
+          <t>Associated Motor Finance Company PLC (COSE:AMF.N0000)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1064,10 +1073,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.0161</v>
+        <v>-0.0759</v>
       </c>
       <c r="E6">
-        <v>0.06509999999999999</v>
+        <v>-0.0245</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1082,85 +1091,82 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>29.2</v>
+        <v>1.07</v>
       </c>
       <c r="L6">
-        <v>0.5087108013937283</v>
+        <v>0.3364779874213836</v>
       </c>
       <c r="M6">
-        <v>2.59</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.02485604606525911</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.0886986301369863</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>2.59</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.02485604606525911</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.0886986301369863</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>4.39</v>
+        <v>0.744</v>
       </c>
       <c r="V6">
-        <v>0.04213051823416506</v>
+        <v>0.2976</v>
       </c>
       <c r="W6">
-        <v>0.115689381933439</v>
+        <v>0.09067796610169492</v>
       </c>
       <c r="X6">
-        <v>0.041828442408154</v>
+        <v>0.08439020585732565</v>
       </c>
       <c r="Y6">
-        <v>0.07386093952528498</v>
+        <v>0.006287760244369264</v>
       </c>
       <c r="Z6">
-        <v>0.1990636379400035</v>
+        <v>0.2037155669442665</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.04420864529133915</v>
+        <v>0.09131737098725778</v>
       </c>
       <c r="AC6">
-        <v>-0.04420864529133915</v>
+        <v>-0.09131737098725778</v>
       </c>
       <c r="AD6">
-        <v>7.81</v>
+        <v>0.279</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>7.81</v>
+        <v>0.279</v>
       </c>
       <c r="AG6">
-        <v>3.42</v>
+        <v>-0.465</v>
       </c>
       <c r="AH6">
-        <v>0.06972591732880992</v>
+        <v>0.1003958258366319</v>
       </c>
       <c r="AI6">
-        <v>0.02839896731027963</v>
+        <v>0.03563673521522545</v>
       </c>
       <c r="AJ6">
-        <v>0.03177847983646162</v>
+        <v>-0.2285012285012285</v>
       </c>
       <c r="AK6">
-        <v>0.0126376468849309</v>
+        <v>-0.06563161609033168</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1177,7 +1183,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HNB Finance PLC (COSE:HNBF.N0000)</t>
+          <t>SMB Finance PLC (COSE:SEMB.N0000)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1185,6 +1191,12 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D7">
+        <v>-0.0287</v>
+      </c>
+      <c r="E7">
+        <v>0.171</v>
+      </c>
       <c r="G7">
         <v>0</v>
       </c>
@@ -1198,10 +1210,10 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>1.86</v>
+        <v>0.107</v>
       </c>
       <c r="L7">
-        <v>0.1184713375796178</v>
+        <v>0.200374531835206</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1225,55 +1237,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>2.11</v>
+        <v>0.417</v>
       </c>
       <c r="V7">
-        <v>0.02425287356321839</v>
+        <v>0.02512048192771084</v>
       </c>
       <c r="W7">
-        <v>0.07294117647058825</v>
+        <v>0.0066875</v>
       </c>
       <c r="X7">
-        <v>0.04286210129892631</v>
+        <v>0.08979191827278235</v>
       </c>
       <c r="Y7">
-        <v>0.03007907517166194</v>
+        <v>-0.08310441827278235</v>
       </c>
       <c r="Z7">
-        <v>0.8722222222222222</v>
+        <v>0.07072847682119207</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.04730194946599909</v>
+        <v>0.1043647914517388</v>
       </c>
       <c r="AC7">
-        <v>-0.04730194946599909</v>
+        <v>-0.1043647914517388</v>
       </c>
       <c r="AD7">
-        <v>11.2</v>
+        <v>4.66</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>11.2</v>
+        <v>4.66</v>
       </c>
       <c r="AG7">
-        <v>9.09</v>
+        <v>4.243</v>
       </c>
       <c r="AH7">
-        <v>0.1140529531568228</v>
+        <v>0.2191909689557855</v>
       </c>
       <c r="AI7">
-        <v>0.3068493150684931</v>
+        <v>0.3379260333575054</v>
       </c>
       <c r="AJ7">
-        <v>0.09459881361223853</v>
+        <v>0.2035695437317085</v>
       </c>
       <c r="AK7">
-        <v>0.2643210235533585</v>
+        <v>0.3172810887609362</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1290,7 +1302,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Commercial Leasing &amp; Finance PLC (COSE:CLC.N0000)</t>
+          <t>LOLC Finance PLC (COSE:LOFC.N0000)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1299,10 +1311,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0955</v>
+        <v>0.221</v>
       </c>
       <c r="E8">
-        <v>0.172</v>
+        <v>0.625</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1317,10 +1329,10 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>19.3</v>
+        <v>46.3</v>
       </c>
       <c r="L8">
-        <v>0.3954918032786885</v>
+        <v>0.6962406015037593</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1344,55 +1356,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>10.1</v>
+        <v>70.8</v>
       </c>
       <c r="V8">
-        <v>0.01074811109928701</v>
+        <v>0.1647661158948103</v>
       </c>
       <c r="W8">
-        <v>0.1859344894026975</v>
+        <v>0.2380462724935732</v>
       </c>
       <c r="X8">
-        <v>0.0427276721987529</v>
+        <v>0.08966357824958962</v>
       </c>
       <c r="Y8">
-        <v>0.1432068172039446</v>
+        <v>0.1483826942439836</v>
       </c>
       <c r="Z8">
-        <v>0.2400393507132317</v>
+        <v>0.3490813648293963</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.04743023565175337</v>
+        <v>0.1094706721303853</v>
       </c>
       <c r="AC8">
-        <v>-0.04743023565175337</v>
+        <v>-0.1094706721303853</v>
       </c>
       <c r="AD8">
-        <v>114.4</v>
+        <v>118.9</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>114.4</v>
+        <v>118.9</v>
       </c>
       <c r="AG8">
-        <v>104.3</v>
+        <v>48.10000000000001</v>
       </c>
       <c r="AH8">
-        <v>0.1085286025993739</v>
+        <v>0.2167335034633613</v>
       </c>
       <c r="AI8">
-        <v>0.4954525768731052</v>
+        <v>0.3336139169472503</v>
       </c>
       <c r="AJ8">
-        <v>0.09990421455938699</v>
+        <v>0.1006697362913353</v>
       </c>
       <c r="AK8">
-        <v>0.4723731884057971</v>
+        <v>0.1684173669467787</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1409,7 +1421,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LOLC Development Finance PLC (COSE:NIFL.N0000)</t>
+          <t>Senkadagala Finance PLC (COSE:SFCL.N0000)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1418,10 +1430,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0867</v>
+        <v>0.0387</v>
       </c>
       <c r="E9">
-        <v>0.139</v>
+        <v>0.016</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1436,82 +1448,85 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>1.66</v>
+        <v>2.66</v>
       </c>
       <c r="L9">
-        <v>0.1349593495934959</v>
+        <v>0.2797055730809674</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>0.331</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.003853317811408615</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0.1244360902255639</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>0.331</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.003853317811408615</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0.1244360902255639</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="V9">
-        <v>0.00264813843733613</v>
+        <v>0.01955762514551804</v>
       </c>
       <c r="W9">
-        <v>0.1136986301369863</v>
+        <v>0.08444444444444445</v>
       </c>
       <c r="X9">
-        <v>0.04279156652663372</v>
+        <v>0.1022427373516955</v>
       </c>
       <c r="Y9">
-        <v>0.07090706361035257</v>
+        <v>-0.01779829290725106</v>
       </c>
       <c r="Z9">
-        <v>0.1513101242465248</v>
+        <v>0.08523032801577343</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.04760117183156748</v>
+        <v>0.1239316483775635</v>
       </c>
       <c r="AC9">
-        <v>-0.04760117183156748</v>
+        <v>-0.1239316483775635</v>
       </c>
       <c r="AD9">
-        <v>47.7</v>
+        <v>57.6</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>47.7</v>
+        <v>57.6</v>
       </c>
       <c r="AG9">
-        <v>46.69</v>
+        <v>55.92</v>
       </c>
       <c r="AH9">
-        <v>0.111162899091121</v>
+        <v>0.4013937282229965</v>
       </c>
       <c r="AI9">
-        <v>0.7607655502392344</v>
+        <v>0.7328244274809161</v>
       </c>
       <c r="AJ9">
-        <v>0.1090658506388844</v>
+        <v>0.3943026371456776</v>
       </c>
       <c r="AK9">
-        <v>0.7568487599286756</v>
+        <v>0.7269890795631825</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1528,7 +1543,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lanka Credit and Business Finance Limited (COSE:LCBF.N0000)</t>
+          <t>Nation Lanka Finance PLC (COSE:CSF.N0000)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1536,6 +1551,9 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D10">
+        <v>-0.335</v>
+      </c>
       <c r="G10">
         <v>0</v>
       </c>
@@ -1549,10 +1567,10 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0.178</v>
+        <v>-1.28</v>
       </c>
       <c r="L10">
-        <v>0.09417989417989418</v>
+        <v>-4.155844155844156</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1561,7 +1579,7 @@
         <v>-0</v>
       </c>
       <c r="O10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P10">
         <v>-0</v>
@@ -1570,61 +1588,61 @@
         <v>-0</v>
       </c>
       <c r="R10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
       <c r="U10">
-        <v>0.884</v>
+        <v>1.14</v>
       </c>
       <c r="V10">
-        <v>0.05815789473684211</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="W10">
-        <v>0.0227330779054917</v>
+        <v>-0.3359580052493438</v>
       </c>
       <c r="X10">
-        <v>0.04359952121469999</v>
+        <v>0.1040399735881835</v>
       </c>
       <c r="Y10">
-        <v>-0.02086644330920829</v>
+        <v>-0.4399979788375273</v>
       </c>
       <c r="Z10">
-        <v>0.1903131608095861</v>
+        <v>0.04071919619249074</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.04906761353458192</v>
+        <v>0.1260264223022821</v>
       </c>
       <c r="AC10">
-        <v>-0.04906761353458192</v>
+        <v>-0.1260264223022821</v>
       </c>
       <c r="AD10">
-        <v>2.54</v>
+        <v>2.9</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>2.54</v>
+        <v>2.9</v>
       </c>
       <c r="AG10">
-        <v>1.656</v>
+        <v>1.76</v>
       </c>
       <c r="AH10">
-        <v>0.1431792559188275</v>
+        <v>0.4208998548621189</v>
       </c>
       <c r="AI10">
-        <v>0.1918429003021148</v>
+        <v>0.773952495329597</v>
       </c>
       <c r="AJ10">
-        <v>0.09824394874228763</v>
+        <v>0.3060869565217391</v>
       </c>
       <c r="AK10">
-        <v>0.1340239559728068</v>
+        <v>0.6751054852320675</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1641,7 +1659,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LOLC Finance PLC (COSE:LOFC.N0000)</t>
+          <t>HNB Finance PLC (COSE:HNBF.N0000)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1649,12 +1667,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D11">
-        <v>0.12</v>
-      </c>
-      <c r="E11">
-        <v>0.392</v>
-      </c>
       <c r="G11">
         <v>0</v>
       </c>
@@ -1668,10 +1680,10 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>35.8</v>
+        <v>-0.879</v>
       </c>
       <c r="L11">
-        <v>0.5311572700296735</v>
+        <v>-0.09052523171987641</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1680,7 +1692,7 @@
         <v>-0</v>
       </c>
       <c r="O11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P11">
         <v>-0</v>
@@ -1689,61 +1701,61 @@
         <v>-0</v>
       </c>
       <c r="R11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
       <c r="U11">
-        <v>100.3</v>
+        <v>1.16</v>
       </c>
       <c r="V11">
-        <v>0.1938538848086587</v>
+        <v>0.058</v>
       </c>
       <c r="W11">
-        <v>0.2098475967174677</v>
+        <v>-0.03474308300395257</v>
       </c>
       <c r="X11">
-        <v>0.0439650186211023</v>
+        <v>0.1062177079212713</v>
       </c>
       <c r="Y11">
-        <v>0.1658825780963654</v>
+        <v>-0.1409607909252238</v>
       </c>
       <c r="Z11">
-        <v>0.238922367954626</v>
+        <v>0.2823495202093632</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.04990041226105906</v>
+        <v>0.1271096148752578</v>
       </c>
       <c r="AC11">
-        <v>-0.04990041226105906</v>
+        <v>-0.1271096148752578</v>
       </c>
       <c r="AD11">
-        <v>96.3</v>
+        <v>15.9</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>96.3</v>
+        <v>15.9</v>
       </c>
       <c r="AG11">
-        <v>-4</v>
+        <v>14.74</v>
       </c>
       <c r="AH11">
-        <v>0.1569170604529901</v>
+        <v>0.4428969359331477</v>
       </c>
       <c r="AI11">
-        <v>0.3311554332874828</v>
+        <v>0.5426621160409556</v>
       </c>
       <c r="AJ11">
-        <v>-0.007791195948578107</v>
+        <v>0.4242947610823258</v>
       </c>
       <c r="AK11">
-        <v>-0.02099737532808399</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1760,7 +1772,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Prime Finance PLC (COSE:GSF.N0000)</t>
+          <t>Softlogic Finance PLC (COSE:CRL.N0000)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1769,10 +1781,7 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.336</v>
-      </c>
-      <c r="E12">
-        <v>0.453</v>
+        <v>-0.504</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1781,16 +1790,16 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0.01584396044898605</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>0.010767569573424</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>0.614</v>
+        <v>-4.1</v>
       </c>
       <c r="L12">
-        <v>0.1811209439528023</v>
+        <v>-32.28346456692913</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1799,7 +1808,7 @@
         <v>-0</v>
       </c>
       <c r="O12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P12">
         <v>-0</v>
@@ -1808,73 +1817,67 @@
         <v>-0</v>
       </c>
       <c r="R12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
       <c r="U12">
-        <v>4.35</v>
+        <v>0.786</v>
       </c>
       <c r="V12">
-        <v>0.3883928571428572</v>
+        <v>0.05171052631578948</v>
       </c>
       <c r="W12">
-        <v>0.06747252747252748</v>
+        <v>-0.1589147286821705</v>
       </c>
       <c r="X12">
-        <v>0.04768329529210028</v>
+        <v>0.1100336460083249</v>
       </c>
       <c r="Y12">
-        <v>0.0197892321804272</v>
+        <v>-0.2689483746904954</v>
       </c>
       <c r="Z12">
-        <v>0.2785207537888199</v>
+        <v>0.003311603650586701</v>
       </c>
       <c r="AA12">
-        <v>0.002998991594063615</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.05546496975308933</v>
+        <v>0.1321222731506645</v>
       </c>
       <c r="AC12">
-        <v>-0.05246597815902571</v>
+        <v>-0.1321222731506645</v>
       </c>
       <c r="AD12">
-        <v>4.07</v>
+        <v>13.9</v>
       </c>
       <c r="AE12">
-        <v>0.1814448703896865</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>4.251444870389687</v>
+        <v>13.9</v>
       </c>
       <c r="AG12">
-        <v>-0.09855512961031287</v>
+        <v>13.114</v>
       </c>
       <c r="AH12">
-        <v>0.2751486936045008</v>
+        <v>0.4776632302405498</v>
       </c>
       <c r="AI12">
-        <v>0.266524123985881</v>
+        <v>0.5791666666666667</v>
       </c>
       <c r="AJ12">
-        <v>-0.008877684910473582</v>
+        <v>0.4631630995267359</v>
       </c>
       <c r="AK12">
-        <v>-0.008495073735328837</v>
+        <v>0.5649177220642716</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
         <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>45.22222222222223</v>
-      </c>
-      <c r="AP12">
-        <v>-1.095056995670143</v>
       </c>
     </row>
     <row r="13">
@@ -1885,7 +1888,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Senkadagala Finance PLC (COSE:SFCL.N0000)</t>
+          <t>People's Merchant Finance PLC (COSE:PMB.N0000)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1893,12 +1896,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D13">
-        <v>0.00459</v>
-      </c>
-      <c r="E13">
-        <v>-0.101</v>
-      </c>
       <c r="G13">
         <v>0</v>
       </c>
@@ -1912,85 +1909,82 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>2.03</v>
+        <v>0.276</v>
       </c>
       <c r="L13">
-        <v>0.1598425196850394</v>
+        <v>0.1550561797752809</v>
       </c>
       <c r="M13">
-        <v>0.451</v>
+        <v>-0</v>
       </c>
       <c r="N13">
-        <v>0.001400621118012422</v>
+        <v>-0</v>
       </c>
       <c r="O13">
-        <v>0.2221674876847291</v>
+        <v>-0</v>
       </c>
       <c r="P13">
-        <v>0.451</v>
+        <v>-0</v>
       </c>
       <c r="Q13">
-        <v>0.001400621118012422</v>
+        <v>-0</v>
       </c>
       <c r="R13">
-        <v>0.2221674876847291</v>
+        <v>-0</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
       <c r="U13">
-        <v>3.02</v>
+        <v>1.01</v>
       </c>
       <c r="V13">
-        <v>0.00937888198757764</v>
+        <v>0.2399049881235154</v>
       </c>
       <c r="W13">
-        <v>0.06999999999999999</v>
+        <v>0.02579439252336449</v>
       </c>
       <c r="X13">
-        <v>0.04534784535696096</v>
+        <v>0.1185311328411344</v>
       </c>
       <c r="Y13">
-        <v>0.02465215464303903</v>
+        <v>-0.09273674031776986</v>
       </c>
       <c r="Z13">
-        <v>0.08411153056493809</v>
+        <v>0.1375579598145286</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.05282340123157967</v>
+        <v>0.1374028455951991</v>
       </c>
       <c r="AC13">
-        <v>-0.05282340123157967</v>
+        <v>-0.1374028455951991</v>
       </c>
       <c r="AD13">
-        <v>83.09999999999999</v>
+        <v>4.97</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>83.09999999999999</v>
+        <v>4.97</v>
       </c>
       <c r="AG13">
-        <v>80.08</v>
+        <v>3.96</v>
       </c>
       <c r="AH13">
-        <v>0.2051345346827944</v>
+        <v>0.5413943355119826</v>
       </c>
       <c r="AI13">
-        <v>0.725130890052356</v>
+        <v>0.3979183346677342</v>
       </c>
       <c r="AJ13">
-        <v>0.1991643454038997</v>
+        <v>0.4847001223990208</v>
       </c>
       <c r="AK13">
-        <v>0.7176913425345044</v>
+        <v>0.3449477351916376</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2007,7 +2001,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sinhaputhra Finance PLC (COSE:SFL.N0000)</t>
+          <t>LB Finance PLC (COSE:LFIN.N0000)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2016,7 +2010,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>-0.102</v>
+        <v>0.132</v>
+      </c>
+      <c r="E14">
+        <v>0.183</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2031,82 +2028,85 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0.276</v>
+        <v>25.1</v>
       </c>
       <c r="L14">
-        <v>0.2358974358974359</v>
+        <v>0.4190317195325543</v>
       </c>
       <c r="M14">
-        <v>-0</v>
+        <v>7.59</v>
       </c>
       <c r="N14">
-        <v>-0</v>
+        <v>0.1258706467661692</v>
       </c>
       <c r="O14">
-        <v>-0</v>
+        <v>0.302390438247012</v>
       </c>
       <c r="P14">
-        <v>-0</v>
+        <v>7.59</v>
       </c>
       <c r="Q14">
-        <v>-0</v>
+        <v>0.1258706467661692</v>
       </c>
       <c r="R14">
-        <v>-0</v>
+        <v>0.302390438247012</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
       <c r="U14">
-        <v>0.207</v>
+        <v>17.5</v>
       </c>
       <c r="V14">
-        <v>0.02487980769230769</v>
+        <v>0.2902155887230514</v>
       </c>
       <c r="W14">
-        <v>0.06418604651162792</v>
+        <v>0.1704005431093008</v>
       </c>
       <c r="X14">
-        <v>0.04579325099764163</v>
+        <v>0.1315159130187751</v>
       </c>
       <c r="Y14">
-        <v>0.01839279551398629</v>
+        <v>0.03888463009052562</v>
       </c>
       <c r="Z14">
-        <v>0.1578521316783594</v>
+        <v>0.2885356454720617</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.05318670618768688</v>
+        <v>0.1449340530227302</v>
       </c>
       <c r="AC14">
-        <v>-0.05318670618768688</v>
+        <v>-0.1449340530227302</v>
       </c>
       <c r="AD14">
-        <v>2.34</v>
+        <v>95.7</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>2.34</v>
+        <v>95.7</v>
       </c>
       <c r="AG14">
-        <v>2.133</v>
+        <v>78.2</v>
       </c>
       <c r="AH14">
-        <v>0.2195121951219512</v>
+        <v>0.6134615384615385</v>
       </c>
       <c r="AI14">
-        <v>0.3633540372670808</v>
+        <v>0.5066172578083642</v>
       </c>
       <c r="AJ14">
-        <v>0.2040562517937434</v>
+        <v>0.5646209386281589</v>
       </c>
       <c r="AK14">
-        <v>0.342210813412482</v>
+        <v>0.456242707117853</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>People's Merchant Finance PLC (COSE:PMB.N0000)</t>
+          <t>Abans Finance PLC (COSE:AFSL.N0000)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2132,7 +2132,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.495</v>
+        <v>0.126</v>
+      </c>
+      <c r="E15">
+        <v>0.29</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2147,10 +2150,10 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0.383</v>
+        <v>1.1</v>
       </c>
       <c r="L15">
-        <v>0.1789719626168224</v>
+        <v>0.2702702702702703</v>
       </c>
       <c r="M15">
         <v>-0</v>
@@ -2174,55 +2177,55 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>1.61</v>
+        <v>0.324</v>
       </c>
       <c r="V15">
-        <v>0.1183823529411765</v>
+        <v>0.07769784172661871</v>
       </c>
       <c r="W15">
-        <v>0.0458133971291866</v>
+        <v>0.1018518518518519</v>
       </c>
       <c r="X15">
-        <v>0.04582857975325774</v>
+        <v>0.1427134536282672</v>
       </c>
       <c r="Y15">
-        <v>-1.518262407113752e-05</v>
+        <v>-0.04086160177641529</v>
       </c>
       <c r="Z15">
-        <v>0.3022598870056497</v>
+        <v>0.242204237086408</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.05376277360085514</v>
+        <v>0.1497547874313097</v>
       </c>
       <c r="AC15">
-        <v>-0.05376277360085514</v>
+        <v>-0.1497547874313097</v>
       </c>
       <c r="AD15">
-        <v>3.85</v>
+        <v>8.08</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>3.85</v>
+        <v>8.08</v>
       </c>
       <c r="AG15">
-        <v>2.24</v>
+        <v>7.756</v>
       </c>
       <c r="AH15">
-        <v>0.2206303724928367</v>
+        <v>0.6595918367346939</v>
       </c>
       <c r="AI15">
-        <v>0.2646048109965636</v>
+        <v>0.5358090185676393</v>
       </c>
       <c r="AJ15">
-        <v>0.1414141414141414</v>
+        <v>0.6503437866845547</v>
       </c>
       <c r="AK15">
-        <v>0.1731066460587326</v>
+        <v>0.5256166982922201</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2239,7 +2242,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Softlogic Finance PLC (COSE:CRL.N0000)</t>
+          <t>Citizens Development Business Finance PLC (COSE:CDB.N0000)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2248,7 +2251,10 @@
         </is>
       </c>
       <c r="D16">
-        <v>-0.1</v>
+        <v>0.209</v>
+      </c>
+      <c r="E16">
+        <v>0.31</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2263,82 +2269,85 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>-1.89</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="L16">
-        <v>-0.4554216867469879</v>
+        <v>0.3726495726495727</v>
       </c>
       <c r="M16">
-        <v>-0</v>
+        <v>0.717</v>
       </c>
       <c r="N16">
-        <v>-0</v>
+        <v>0.02219814241486068</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>0.08222477064220182</v>
       </c>
       <c r="P16">
-        <v>-0</v>
+        <v>0.717</v>
       </c>
       <c r="Q16">
-        <v>-0</v>
+        <v>0.02219814241486068</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>0.08222477064220182</v>
       </c>
       <c r="S16">
         <v>0</v>
       </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
       <c r="U16">
-        <v>1.05</v>
+        <v>5.94</v>
       </c>
       <c r="V16">
-        <v>0.03322784810126582</v>
+        <v>0.1839009287925697</v>
       </c>
       <c r="W16">
-        <v>-0.1766355140186916</v>
+        <v>0.1156498673740053</v>
       </c>
       <c r="X16">
-        <v>0.04865935219692864</v>
+        <v>0.1569665201873306</v>
       </c>
       <c r="Y16">
-        <v>-0.2252948662156202</v>
+        <v>-0.04131665281332526</v>
       </c>
       <c r="Z16">
-        <v>0.1747294850743127</v>
+        <v>0.1201972467639203</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.0568752112191014</v>
+        <v>0.1544460367999475</v>
       </c>
       <c r="AC16">
-        <v>-0.0568752112191014</v>
+        <v>-0.1544460367999475</v>
       </c>
       <c r="AD16">
-        <v>13.6</v>
+        <v>77</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>13.6</v>
+        <v>77</v>
       </c>
       <c r="AG16">
-        <v>12.55</v>
+        <v>71.06</v>
       </c>
       <c r="AH16">
-        <v>0.3008849557522124</v>
+        <v>0.7044830741079597</v>
       </c>
       <c r="AI16">
-        <v>0.3451776649746193</v>
+        <v>0.6150159744408945</v>
       </c>
       <c r="AJ16">
-        <v>0.2842582106455266</v>
+        <v>0.6875</v>
       </c>
       <c r="AK16">
-        <v>0.3272490221642764</v>
+        <v>0.5958410196209961</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2355,7 +2364,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nation Lanka Finance PLC (COSE:CSF.N0000)</t>
+          <t>Orient Finance PLC (COSE:BFN.N0000)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2364,7 +2373,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>-0.232</v>
+        <v>0.0779</v>
+      </c>
+      <c r="E17">
+        <v>0.242</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2379,10 +2391,10 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>-1.62</v>
+        <v>0.747</v>
       </c>
       <c r="L17">
-        <v>-1.031847133757962</v>
+        <v>0.19453125</v>
       </c>
       <c r="M17">
         <v>-0</v>
@@ -2391,7 +2403,7 @@
         <v>-0</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P17">
         <v>-0</v>
@@ -2400,61 +2412,61 @@
         <v>-0</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
       <c r="U17">
-        <v>0.856</v>
+        <v>0.602</v>
       </c>
       <c r="V17">
-        <v>0.09873125720876585</v>
+        <v>0.1233606557377049</v>
       </c>
       <c r="W17">
-        <v>-0.278829604130809</v>
+        <v>0.04819354838709677</v>
       </c>
       <c r="X17">
-        <v>0.05060696713051173</v>
+        <v>0.1528206819902101</v>
       </c>
       <c r="Y17">
-        <v>-0.3294365712613207</v>
+        <v>-0.1046271336031133</v>
       </c>
       <c r="Z17">
-        <v>0.1608276992419586</v>
+        <v>0.1391808626313882</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.06062801702272787</v>
+        <v>0.1552146789939642</v>
       </c>
       <c r="AC17">
-        <v>-0.06062801702272787</v>
+        <v>-0.1552146789939642</v>
       </c>
       <c r="AD17">
-        <v>4.61</v>
+        <v>11</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>4.61</v>
+        <v>11</v>
       </c>
       <c r="AG17">
-        <v>3.754</v>
+        <v>10.398</v>
       </c>
       <c r="AH17">
-        <v>0.3471385542168675</v>
+        <v>0.6926952141057935</v>
       </c>
       <c r="AI17">
-        <v>0.5475059382422803</v>
+        <v>0.5453644025780863</v>
       </c>
       <c r="AJ17">
-        <v>0.3021571152607856</v>
+        <v>0.6805864641968844</v>
       </c>
       <c r="AK17">
-        <v>0.4962982548915918</v>
+        <v>0.5313777596075225</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2471,7 +2483,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LB Finance PLC (COSE:LFIN.N0000)</t>
+          <t>People's Leasing &amp; Finance PLC (COSE:PLC.N0000)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2480,10 +2492,10 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.122</v>
+        <v>0.066</v>
       </c>
       <c r="E18">
-        <v>0.147</v>
+        <v>0.048</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2498,85 +2510,82 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>39.8</v>
+        <v>13.1</v>
       </c>
       <c r="L18">
-        <v>0.4274973147153598</v>
+        <v>0.229020979020979</v>
       </c>
       <c r="M18">
-        <v>19.4</v>
+        <v>-0</v>
       </c>
       <c r="N18">
-        <v>0.1044695745826602</v>
+        <v>-0</v>
       </c>
       <c r="O18">
-        <v>0.4874371859296482</v>
+        <v>-0</v>
       </c>
       <c r="P18">
-        <v>19.4</v>
+        <v>-0</v>
       </c>
       <c r="Q18">
-        <v>0.1044695745826602</v>
+        <v>-0</v>
       </c>
       <c r="R18">
-        <v>0.4874371859296482</v>
+        <v>-0</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
       <c r="U18">
-        <v>59.3</v>
+        <v>17.6</v>
       </c>
       <c r="V18">
-        <v>0.3193322563274098</v>
+        <v>0.6330935251798562</v>
       </c>
       <c r="W18">
-        <v>0.2886149383611312</v>
+        <v>0.06619504800404244</v>
       </c>
       <c r="X18">
-        <v>0.0527658384610625</v>
+        <v>0.1798613946293333</v>
       </c>
       <c r="Y18">
-        <v>0.2358490999000687</v>
+        <v>-0.1136663466252908</v>
       </c>
       <c r="Z18">
-        <v>0.4178635547576302</v>
+        <v>0.1591984414138602</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.06322886343623435</v>
+        <v>0.1554194212945281</v>
       </c>
       <c r="AC18">
-        <v>-0.06322886343623435</v>
+        <v>-0.1554194212945281</v>
       </c>
       <c r="AD18">
-        <v>119.6</v>
+        <v>86.2</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>119.6</v>
+        <v>86.2</v>
       </c>
       <c r="AG18">
-        <v>60.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="AH18">
-        <v>0.3917458237798886</v>
+        <v>0.756140350877193</v>
       </c>
       <c r="AI18">
-        <v>0.4481079055826152</v>
+        <v>0.4089184060721063</v>
       </c>
       <c r="AJ18">
-        <v>0.2451219512195122</v>
+        <v>0.7116182572614108</v>
       </c>
       <c r="AK18">
-        <v>0.2904624277456647</v>
+        <v>0.3550724637681159</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2593,7 +2602,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Abans Finance PLC (COSE:AFSL.N0000)</t>
+          <t>Merchant Bank of Sri Lanka &amp; Finance PLC (COSE:MBSL.N0000)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2602,10 +2611,7 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.111</v>
-      </c>
-      <c r="E19">
-        <v>0.31</v>
+        <v>0.0375</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2620,10 +2626,10 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>1.92</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="L19">
-        <v>0.2981366459627329</v>
+        <v>0.01025029797377831</v>
       </c>
       <c r="M19">
         <v>-0</v>
@@ -2647,55 +2653,55 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>0.896</v>
+        <v>2.01</v>
       </c>
       <c r="V19">
-        <v>0.08533333333333333</v>
+        <v>0.4144329896907216</v>
       </c>
       <c r="W19">
-        <v>0.2086956521739131</v>
+        <v>0.004257425742574257</v>
       </c>
       <c r="X19">
-        <v>0.05301747682462811</v>
+        <v>0.1618271332939448</v>
       </c>
       <c r="Y19">
-        <v>0.155678175349285</v>
+        <v>-0.1575697075513706</v>
       </c>
       <c r="Z19">
-        <v>0.4313462826523778</v>
+        <v>0.2279891304347826</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.06350907356414243</v>
+        <v>0.155775110019977</v>
       </c>
       <c r="AC19">
-        <v>-0.06350907356414243</v>
+        <v>-0.155775110019977</v>
       </c>
       <c r="AD19">
-        <v>6.9</v>
+        <v>12.3</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>6.9</v>
+        <v>12.3</v>
       </c>
       <c r="AG19">
-        <v>6.004</v>
+        <v>10.29</v>
       </c>
       <c r="AH19">
-        <v>0.3965517241379311</v>
+        <v>0.7172011661807581</v>
       </c>
       <c r="AI19">
-        <v>0.3898305084745762</v>
+        <v>0.4979757085020243</v>
       </c>
       <c r="AJ19">
-        <v>0.3637905962190984</v>
+        <v>0.679656538969617</v>
       </c>
       <c r="AK19">
-        <v>0.3572958819328731</v>
+        <v>0.4535037461436757</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2712,7 +2718,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LOLC Holdings PLC (COSE:LOLC.N0000)</t>
+          <t>Housing Development Finance Corporation Bank of Sri Lanka (COSE:HDFC.N0000)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2721,10 +2727,10 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.176</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="E20">
-        <v>0.204</v>
+        <v>0.061</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2739,82 +2745,85 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>117.2</v>
+        <v>1.14</v>
       </c>
       <c r="L20">
-        <v>0.1967433271781098</v>
+        <v>0.1302857142857143</v>
       </c>
       <c r="M20">
-        <v>-0</v>
+        <v>0.046</v>
       </c>
       <c r="N20">
-        <v>-0</v>
+        <v>0.009387755102040816</v>
       </c>
       <c r="O20">
-        <v>-0</v>
+        <v>0.04035087719298246</v>
       </c>
       <c r="P20">
-        <v>-0</v>
+        <v>0.046</v>
       </c>
       <c r="Q20">
-        <v>-0</v>
+        <v>0.009387755102040816</v>
       </c>
       <c r="R20">
-        <v>-0</v>
+        <v>0.04035087719298246</v>
       </c>
       <c r="S20">
         <v>0</v>
       </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
       <c r="U20">
-        <v>342.1</v>
+        <v>0.696</v>
       </c>
       <c r="V20">
-        <v>0.1257165956195796</v>
+        <v>0.1420408163265306</v>
       </c>
       <c r="W20">
-        <v>0.2053618363413352</v>
+        <v>0.03725490196078431</v>
       </c>
       <c r="X20">
-        <v>0.05357954151715724</v>
+        <v>0.1662152122207784</v>
       </c>
       <c r="Y20">
-        <v>0.151782294824178</v>
+        <v>-0.128960310259994</v>
       </c>
       <c r="Z20">
-        <v>0.3450333043730091</v>
+        <v>0.1567257746731148</v>
       </c>
       <c r="AA20">
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.06411924319197058</v>
+        <v>0.1589822152635667</v>
       </c>
       <c r="AC20">
-        <v>-0.06411924319197058</v>
+        <v>-0.1589822152635667</v>
       </c>
       <c r="AD20">
-        <v>1867.8</v>
+        <v>13.1</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>1867.8</v>
+        <v>13.1</v>
       </c>
       <c r="AG20">
-        <v>1525.7</v>
+        <v>12.404</v>
       </c>
       <c r="AH20">
-        <v>0.4070167792547396</v>
+        <v>0.7277777777777777</v>
       </c>
       <c r="AI20">
-        <v>0.601023264793899</v>
+        <v>0.4212218649517684</v>
       </c>
       <c r="AJ20">
-        <v>0.3592502766723963</v>
+        <v>0.7168284789644012</v>
       </c>
       <c r="AK20">
-        <v>0.5516705235753543</v>
+        <v>0.4079726351795817</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -2831,7 +2840,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Orient Finance PLC (COSE:BFN.N0000)</t>
+          <t>LOLC Holdings PLC (COSE:LOLC.N0000)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2840,10 +2849,10 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.0384</v>
+        <v>0.184</v>
       </c>
       <c r="E21">
-        <v>0.0138</v>
+        <v>0.315</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2858,10 +2867,10 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>2.08</v>
+        <v>184.1</v>
       </c>
       <c r="L21">
-        <v>0.2913165266106443</v>
+        <v>0.405595946243666</v>
       </c>
       <c r="M21">
         <v>-0</v>
@@ -2885,55 +2894,55 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>1.98</v>
+        <v>405.8</v>
       </c>
       <c r="V21">
-        <v>0.1192771084337349</v>
+        <v>0.7882672882672883</v>
       </c>
       <c r="W21">
-        <v>0.143448275862069</v>
+        <v>0.2484480431848853</v>
       </c>
       <c r="X21">
-        <v>0.05995412293249092</v>
+        <v>0.178269977658132</v>
       </c>
       <c r="Y21">
-        <v>0.08349415292957804</v>
+        <v>0.07017806552675332</v>
       </c>
       <c r="Z21">
-        <v>0.2636632200886262</v>
+        <v>0.2002470551903648</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.06980173978121987</v>
+        <v>0.1617059735501705</v>
       </c>
       <c r="AC21">
-        <v>-0.06980173978121987</v>
+        <v>-0.1617059735501705</v>
       </c>
       <c r="AD21">
-        <v>16.9</v>
+        <v>1570.6</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>16.9</v>
+        <v>1570.6</v>
       </c>
       <c r="AG21">
-        <v>14.92</v>
+        <v>1164.8</v>
       </c>
       <c r="AH21">
-        <v>0.5044776119402985</v>
+        <v>0.7531408842428312</v>
       </c>
       <c r="AI21">
-        <v>0.5216049382716049</v>
+        <v>0.5491032409187847</v>
       </c>
       <c r="AJ21">
-        <v>0.4733502538071065</v>
+        <v>0.6934984520123839</v>
       </c>
       <c r="AK21">
-        <v>0.4904667981591058</v>
+        <v>0.47455693623956</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -2950,7 +2959,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Associated Motor Finance Company PLC (COSE:AMF.N0000)</t>
+          <t>Commercial Credit and Finance PLC (COSE:COCR.N0000)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2959,7 +2968,10 @@
         </is>
       </c>
       <c r="D22">
-        <v>-0.0157</v>
+        <v>0.0449</v>
+      </c>
+      <c r="E22">
+        <v>0.0882</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -2974,82 +2986,85 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>-0.098</v>
+        <v>11.9</v>
       </c>
       <c r="L22">
-        <v>-0.02033195020746888</v>
+        <v>0.3459302325581395</v>
       </c>
       <c r="M22">
-        <v>-0</v>
+        <v>2.61</v>
       </c>
       <c r="N22">
-        <v>-0</v>
+        <v>0.1338461538461538</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>0.2193277310924369</v>
       </c>
       <c r="P22">
-        <v>-0</v>
+        <v>2.61</v>
       </c>
       <c r="Q22">
-        <v>-0</v>
+        <v>0.1338461538461538</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>0.2193277310924369</v>
       </c>
       <c r="S22">
         <v>0</v>
       </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
       <c r="U22">
-        <v>3.76</v>
+        <v>5.82</v>
       </c>
       <c r="V22">
-        <v>0.4947368421052631</v>
+        <v>0.2984615384615385</v>
       </c>
       <c r="W22">
-        <v>-0.009245283018867925</v>
+        <v>0.1463714637146372</v>
       </c>
       <c r="X22">
-        <v>0.06441150520733362</v>
+        <v>0.1804116908528859</v>
       </c>
       <c r="Y22">
-        <v>-0.07365678822620154</v>
+        <v>-0.03404022713824878</v>
       </c>
       <c r="Z22">
-        <v>0.2449186991869919</v>
+        <v>0.1983852364475202</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.07277986168292791</v>
+        <v>0.1621376581977914</v>
       </c>
       <c r="AC22">
-        <v>-0.07277986168292791</v>
+        <v>-0.1621376581977914</v>
       </c>
       <c r="AD22">
-        <v>9.5</v>
+        <v>60.8</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>9.5</v>
+        <v>60.8</v>
       </c>
       <c r="AG22">
-        <v>5.74</v>
+        <v>54.98</v>
       </c>
       <c r="AH22">
-        <v>0.5555555555555555</v>
+        <v>0.7571606475716065</v>
       </c>
       <c r="AI22">
-        <v>0.4460093896713615</v>
+        <v>0.5404444444444444</v>
       </c>
       <c r="AJ22">
-        <v>0.4302848575712144</v>
+        <v>0.7381847475832439</v>
       </c>
       <c r="AK22">
-        <v>0.3272519954389966</v>
+        <v>0.5153730783652043</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3066,7 +3081,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>People's Leasing &amp; Finance PLC (COSE:PLC.N0000)</t>
+          <t>Singer Finance (Lanka) PLC (COSE:SFIN.N0000)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3075,10 +3090,10 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.0536</v>
+        <v>0.146</v>
       </c>
       <c r="E23">
-        <v>0.009820000000000001</v>
+        <v>0.0864</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3087,34 +3102,34 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>0.003615376258991926</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>0.002317127511444825</v>
       </c>
       <c r="K23">
-        <v>23.9</v>
+        <v>1.55</v>
       </c>
       <c r="L23">
-        <v>0.2526427061310782</v>
+        <v>0.181924882629108</v>
       </c>
       <c r="M23">
-        <v>0.002</v>
+        <v>0.438</v>
       </c>
       <c r="N23">
-        <v>2.010050251256282e-05</v>
+        <v>0.08036697247706422</v>
       </c>
       <c r="O23">
-        <v>8.368200836820084e-05</v>
+        <v>0.2825806451612903</v>
       </c>
       <c r="P23">
-        <v>0.002</v>
+        <v>0.438</v>
       </c>
       <c r="Q23">
-        <v>2.010050251256282e-05</v>
+        <v>0.08036697247706422</v>
       </c>
       <c r="R23">
-        <v>8.368200836820084e-05</v>
+        <v>0.2825806451612903</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -3123,61 +3138,67 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>9.9</v>
+        <v>1.28</v>
       </c>
       <c r="V23">
-        <v>0.09949748743718594</v>
+        <v>0.2348623853211009</v>
       </c>
       <c r="W23">
-        <v>0.1276027762947143</v>
+        <v>0.07045454545454545</v>
       </c>
       <c r="X23">
-        <v>0.07347526611551111</v>
+        <v>0.249788916745079</v>
       </c>
       <c r="Y23">
-        <v>0.05412751017920323</v>
+        <v>-0.1793343712905336</v>
       </c>
       <c r="Z23">
-        <v>0.2986111111111111</v>
+        <v>0.1250715914278277</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>0.0002898068253976064</v>
       </c>
       <c r="AB23">
-        <v>0.07505019830571966</v>
+        <v>0.1637928205547931</v>
       </c>
       <c r="AC23">
-        <v>-0.07505019830571966</v>
+        <v>-0.1635030137293955</v>
       </c>
       <c r="AD23">
-        <v>171.3</v>
+        <v>28.8</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>0.03098497136694392</v>
       </c>
       <c r="AF23">
-        <v>171.3</v>
+        <v>28.83098497136695</v>
       </c>
       <c r="AG23">
-        <v>161.4</v>
+        <v>27.55098497136694</v>
       </c>
       <c r="AH23">
-        <v>0.6325701624815362</v>
+        <v>0.8410197371938964</v>
       </c>
       <c r="AI23">
-        <v>0.4477260846837428</v>
+        <v>0.6892255822114057</v>
       </c>
       <c r="AJ23">
-        <v>0.6186278267535454</v>
+        <v>0.8348534140805599</v>
       </c>
       <c r="AK23">
-        <v>0.4330560772739468</v>
+        <v>0.6794159251821059</v>
       </c>
       <c r="AL23">
         <v>0</v>
       </c>
       <c r="AM23">
         <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>778.3783783783784</v>
+      </c>
+      <c r="AP23">
+        <v>744.6212154423499</v>
       </c>
     </row>
     <row r="24">
@@ -3188,7 +3209,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Merchant Bank of Sri Lanka &amp; Finance PLC (COSE:MBSL.N0000)</t>
+          <t>Vallibel Finance PLC (COSE:VFIN.N0000)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3197,10 +3218,10 @@
         </is>
       </c>
       <c r="D24">
-        <v>-0.00265</v>
+        <v>0.168</v>
       </c>
       <c r="E24">
-        <v>0.0278</v>
+        <v>0.209</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3215,82 +3236,85 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>1.39</v>
+        <v>5.91</v>
       </c>
       <c r="L24">
-        <v>0.1139344262295082</v>
+        <v>0.3993243243243243</v>
       </c>
       <c r="M24">
-        <v>-0</v>
+        <v>1.29</v>
       </c>
       <c r="N24">
-        <v>-0</v>
+        <v>0.08958333333333333</v>
       </c>
       <c r="O24">
-        <v>-0</v>
+        <v>0.2182741116751269</v>
       </c>
       <c r="P24">
-        <v>-0</v>
+        <v>1.29</v>
       </c>
       <c r="Q24">
-        <v>-0</v>
+        <v>0.08958333333333333</v>
       </c>
       <c r="R24">
-        <v>-0</v>
+        <v>0.2182741116751269</v>
       </c>
       <c r="S24">
         <v>0</v>
       </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
       <c r="U24">
-        <v>12.3</v>
+        <v>3.04</v>
       </c>
       <c r="V24">
-        <v>0.803921568627451</v>
+        <v>0.2111111111111111</v>
       </c>
       <c r="W24">
-        <v>0.1572398190045249</v>
+        <v>0.1293216630196936</v>
       </c>
       <c r="X24">
-        <v>0.0766902104925785</v>
+        <v>0.2265500374880186</v>
       </c>
       <c r="Y24">
-        <v>0.08054960851194638</v>
+        <v>-0.09722837446832497</v>
       </c>
       <c r="Z24">
-        <v>0.3149199793495095</v>
+        <v>0.1138461538461538</v>
       </c>
       <c r="AA24">
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.07621603525129828</v>
+        <v>0.168910144354098</v>
       </c>
       <c r="AC24">
-        <v>-0.07621603525129828</v>
+        <v>-0.168910144354098</v>
       </c>
       <c r="AD24">
-        <v>28.9</v>
+        <v>65.7</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>28.9</v>
+        <v>65.7</v>
       </c>
       <c r="AG24">
-        <v>16.6</v>
+        <v>62.66</v>
       </c>
       <c r="AH24">
-        <v>0.6538461538461537</v>
+        <v>0.8202247191011235</v>
       </c>
       <c r="AI24">
-        <v>0.5622568093385214</v>
+        <v>0.698936170212766</v>
       </c>
       <c r="AJ24">
-        <v>0.5203761755485893</v>
+        <v>0.8131326239294057</v>
       </c>
       <c r="AK24">
-        <v>0.4245524296675192</v>
+        <v>0.6888742304309586</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -3307,7 +3331,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Singer Finance (Lanka) PLC (COSE:SFIN.N0000)</t>
+          <t>Alliance Finance Company PLC (COSE:ALLI.N0000)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3316,10 +3340,10 @@
         </is>
       </c>
       <c r="D25">
-        <v>0.122</v>
+        <v>0.138</v>
       </c>
       <c r="E25">
-        <v>0.0271</v>
+        <v>0.156</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3328,34 +3352,34 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>0.004730069629250708</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>0.003189729951713734</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>2.35</v>
+        <v>3.71</v>
       </c>
       <c r="L25">
-        <v>0.18359375</v>
+        <v>0.2348101265822785</v>
       </c>
       <c r="M25">
-        <v>0.801</v>
+        <v>1.35</v>
       </c>
       <c r="N25">
-        <v>0.04684210526315789</v>
+        <v>0.2581261950286807</v>
       </c>
       <c r="O25">
-        <v>0.3408510638297872</v>
+        <v>0.3638814016172507</v>
       </c>
       <c r="P25">
-        <v>0.801</v>
+        <v>1.35</v>
       </c>
       <c r="Q25">
-        <v>0.04684210526315789</v>
+        <v>0.2581261950286807</v>
       </c>
       <c r="R25">
-        <v>0.3408510638297872</v>
+        <v>0.3638814016172507</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -3364,67 +3388,61 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="V25">
-        <v>0.1058479532163743</v>
+        <v>0.3652007648183556</v>
       </c>
       <c r="W25">
-        <v>0.1063348416289593</v>
+        <v>0.1224422442244224</v>
       </c>
       <c r="X25">
-        <v>0.09429880170760463</v>
+        <v>0.4912156345071501</v>
       </c>
       <c r="Y25">
-        <v>0.01203603992135464</v>
+        <v>-0.3687733902827276</v>
       </c>
       <c r="Z25">
-        <v>0.1764123570528203</v>
+        <v>0.1460933888118354</v>
       </c>
       <c r="AA25">
-        <v>0.0005627077791437985</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>0.0807832142088976</v>
+        <v>0.1777824286357459</v>
       </c>
       <c r="AC25">
-        <v>-0.0802205064297538</v>
+        <v>-0.1777824286357459</v>
       </c>
       <c r="AD25">
-        <v>47.9</v>
+        <v>67.2</v>
       </c>
       <c r="AE25">
-        <v>0.06727554372795466</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>47.96727554372795</v>
+        <v>67.2</v>
       </c>
       <c r="AG25">
-        <v>46.15727554372795</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="AH25">
-        <v>0.7371950822113631</v>
+        <v>0.9277923512356758</v>
       </c>
       <c r="AI25">
-        <v>0.6855672908651345</v>
+        <v>0.7823050058207217</v>
       </c>
       <c r="AJ25">
-        <v>0.7296753637740965</v>
+        <v>0.9258366420873511</v>
       </c>
       <c r="AK25">
-        <v>0.6772171448389928</v>
+        <v>0.7773544469579712</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
         <v>0</v>
-      </c>
-      <c r="AN25">
-        <v>647.2972972972973</v>
-      </c>
-      <c r="AP25">
-        <v>623.7469668071344</v>
       </c>
     </row>
     <row r="26">
@@ -3435,7 +3453,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vallibel Finance PLC (COSE:VFIN.N0000)</t>
+          <t>Asia Asset Finance PLC (COSE:AAF.N0000)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3444,10 +3462,10 @@
         </is>
       </c>
       <c r="D26">
-        <v>0.219</v>
+        <v>0.105</v>
       </c>
       <c r="E26">
-        <v>0.321</v>
+        <v>-0.0217</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3462,813 +3480,87 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>12.6</v>
+        <v>0.641</v>
       </c>
       <c r="L26">
-        <v>0.4772727272727273</v>
+        <v>0.1405701754385965</v>
       </c>
       <c r="M26">
-        <v>1.77</v>
+        <v>-0</v>
       </c>
       <c r="N26">
-        <v>0.03822894168466523</v>
+        <v>-0</v>
       </c>
       <c r="O26">
-        <v>0.1404761904761905</v>
+        <v>-0</v>
       </c>
       <c r="P26">
-        <v>1.77</v>
+        <v>-0</v>
       </c>
       <c r="Q26">
-        <v>0.03822894168466523</v>
+        <v>-0</v>
       </c>
       <c r="R26">
-        <v>0.1404761904761905</v>
+        <v>-0</v>
       </c>
       <c r="S26">
         <v>0</v>
       </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
       <c r="U26">
-        <v>18.6</v>
+        <v>3.59</v>
       </c>
       <c r="V26">
-        <v>0.4017278617710583</v>
+        <v>1.380769230769231</v>
       </c>
       <c r="W26">
-        <v>0.3342175066312997</v>
+        <v>0.04783582089552239</v>
       </c>
       <c r="X26">
-        <v>0.08310110366432812</v>
+        <v>0.3842516638279827</v>
       </c>
       <c r="Y26">
-        <v>0.2511164029669716</v>
+        <v>-0.3364158429324603</v>
       </c>
       <c r="Z26">
-        <v>0.2767295597484277</v>
+        <v>0.1195595175668589</v>
       </c>
       <c r="AA26">
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.08059994619237665</v>
+        <v>0.17798864032962</v>
       </c>
       <c r="AC26">
-        <v>-0.08059994619237665</v>
+        <v>-0.17798864032962</v>
       </c>
       <c r="AD26">
-        <v>102.9</v>
+        <v>24.7</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>102.9</v>
+        <v>24.7</v>
       </c>
       <c r="AG26">
-        <v>84.30000000000001</v>
+        <v>21.11</v>
       </c>
       <c r="AH26">
-        <v>0.6896782841823057</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="AI26">
-        <v>0.6924629878869447</v>
+        <v>0.758133824432167</v>
       </c>
       <c r="AJ26">
-        <v>0.6454823889739663</v>
+        <v>0.8903416280050611</v>
       </c>
       <c r="AK26">
-        <v>0.6484615384615385</v>
+        <v>0.7281821317695757</v>
       </c>
       <c r="AL26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Sri Lanka</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Commercial Credit and Finance PLC (COSE:COCR.N0000)</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D27">
-        <v>0.00796</v>
-      </c>
-      <c r="E27">
-        <v>0.03240000000000001</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>15.1</v>
-      </c>
-      <c r="L27">
-        <v>0.3205944798301486</v>
-      </c>
-      <c r="M27">
-        <v>2.39</v>
-      </c>
-      <c r="N27">
-        <v>0.05010482180293501</v>
-      </c>
-      <c r="O27">
-        <v>0.1582781456953642</v>
-      </c>
-      <c r="P27">
-        <v>2.39</v>
-      </c>
-      <c r="Q27">
-        <v>0.05010482180293501</v>
-      </c>
-      <c r="R27">
-        <v>0.1582781456953642</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27">
-        <v>17.6</v>
-      </c>
-      <c r="V27">
-        <v>0.3689727463312369</v>
-      </c>
-      <c r="W27">
-        <v>0.1845965770171149</v>
-      </c>
-      <c r="X27">
-        <v>0.08458726130769909</v>
-      </c>
-      <c r="Y27">
-        <v>0.1000093157094158</v>
-      </c>
-      <c r="Z27">
-        <v>0.2360902255639098</v>
-      </c>
-      <c r="AA27">
-        <v>0</v>
-      </c>
-      <c r="AB27">
-        <v>0.08102395270198598</v>
-      </c>
-      <c r="AC27">
-        <v>-0.08102395270198598</v>
-      </c>
-      <c r="AD27">
-        <v>109.7</v>
-      </c>
-      <c r="AE27">
-        <v>0</v>
-      </c>
-      <c r="AF27">
-        <v>109.7</v>
-      </c>
-      <c r="AG27">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="AH27">
-        <v>0.6969504447268107</v>
-      </c>
-      <c r="AI27">
-        <v>0.5743455497382199</v>
-      </c>
-      <c r="AJ27">
-        <v>0.6587982832618025</v>
-      </c>
-      <c r="AK27">
-        <v>0.5311418685121108</v>
-      </c>
-      <c r="AL27">
-        <v>0</v>
-      </c>
-      <c r="AM27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Sri Lanka</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Citizens Development Business Finance PLC (COSE:CDB.N0000)</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D28">
-        <v>0.171</v>
-      </c>
-      <c r="E28">
-        <v>0.231</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>14.7</v>
-      </c>
-      <c r="L28">
-        <v>0.4236311239193083</v>
-      </c>
-      <c r="M28">
-        <v>2.62</v>
-      </c>
-      <c r="N28">
-        <v>0.04720720720720721</v>
-      </c>
-      <c r="O28">
-        <v>0.1782312925170068</v>
-      </c>
-      <c r="P28">
-        <v>2.62</v>
-      </c>
-      <c r="Q28">
-        <v>0.04720720720720721</v>
-      </c>
-      <c r="R28">
-        <v>0.1782312925170068</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-      <c r="U28">
-        <v>7</v>
-      </c>
-      <c r="V28">
-        <v>0.1261261261261261</v>
-      </c>
-      <c r="W28">
-        <v>0.2230652503793626</v>
-      </c>
-      <c r="X28">
-        <v>0.08453934759618982</v>
-      </c>
-      <c r="Y28">
-        <v>0.1385259027831728</v>
-      </c>
-      <c r="Z28">
-        <v>0.1505488307518764</v>
-      </c>
-      <c r="AA28">
-        <v>0</v>
-      </c>
-      <c r="AB28">
-        <v>0.0826238573850962</v>
-      </c>
-      <c r="AC28">
-        <v>-0.0826238573850962</v>
-      </c>
-      <c r="AD28">
-        <v>127.5</v>
-      </c>
-      <c r="AE28">
-        <v>0</v>
-      </c>
-      <c r="AF28">
-        <v>127.5</v>
-      </c>
-      <c r="AG28">
-        <v>120.5</v>
-      </c>
-      <c r="AH28">
-        <v>0.6967213114754098</v>
-      </c>
-      <c r="AI28">
-        <v>0.6283883686545096</v>
-      </c>
-      <c r="AJ28">
-        <v>0.6846590909090909</v>
-      </c>
-      <c r="AK28">
-        <v>0.6151097498723839</v>
-      </c>
-      <c r="AL28">
-        <v>0</v>
-      </c>
-      <c r="AM28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Sri Lanka</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Housing Development Finance Corporation Bank of Sri Lanka (COSE:HDFC.N0000)</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D29">
-        <v>0.0645</v>
-      </c>
-      <c r="E29">
-        <v>0.117</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>3.05</v>
-      </c>
-      <c r="L29">
-        <v>0.2033333333333333</v>
-      </c>
-      <c r="M29">
-        <v>0.06470000000000001</v>
-      </c>
-      <c r="N29">
-        <v>0.006649537512846866</v>
-      </c>
-      <c r="O29">
-        <v>0.02121311475409837</v>
-      </c>
-      <c r="P29">
-        <v>0.06470000000000001</v>
-      </c>
-      <c r="Q29">
-        <v>0.006649537512846866</v>
-      </c>
-      <c r="R29">
-        <v>0.02121311475409837</v>
-      </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
-      <c r="U29">
-        <v>2.17</v>
-      </c>
-      <c r="V29">
-        <v>0.2230215827338129</v>
-      </c>
-      <c r="W29">
-        <v>0.101328903654485</v>
-      </c>
-      <c r="X29">
-        <v>0.09450884550055978</v>
-      </c>
-      <c r="Y29">
-        <v>0.006820058153925251</v>
-      </c>
-      <c r="Z29">
-        <v>0.2069821995308403</v>
-      </c>
-      <c r="AA29">
-        <v>0</v>
-      </c>
-      <c r="AB29">
-        <v>0.08341431863123346</v>
-      </c>
-      <c r="AC29">
-        <v>-0.08341431863123346</v>
-      </c>
-      <c r="AD29">
-        <v>27.4</v>
-      </c>
-      <c r="AE29">
-        <v>0</v>
-      </c>
-      <c r="AF29">
-        <v>27.4</v>
-      </c>
-      <c r="AG29">
-        <v>25.23</v>
-      </c>
-      <c r="AH29">
-        <v>0.7379477511446271</v>
-      </c>
-      <c r="AI29">
-        <v>0.4724137931034483</v>
-      </c>
-      <c r="AJ29">
-        <v>0.7216819221967964</v>
-      </c>
-      <c r="AK29">
-        <v>0.4519075765717356</v>
-      </c>
-      <c r="AL29">
-        <v>0</v>
-      </c>
-      <c r="AM29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Sri Lanka</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Bimputh Finance PLC (COSE:BLI.N0000)</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D30">
-        <v>-0.295</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>-0.279</v>
-      </c>
-      <c r="L30">
-        <v>-0.1732919254658385</v>
-      </c>
-      <c r="M30">
-        <v>-0</v>
-      </c>
-      <c r="N30">
-        <v>-0</v>
-      </c>
-      <c r="O30">
-        <v>0</v>
-      </c>
-      <c r="P30">
-        <v>-0</v>
-      </c>
-      <c r="Q30">
-        <v>-0</v>
-      </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="U30">
-        <v>0.401</v>
-      </c>
-      <c r="V30">
-        <v>0.09325581395348838</v>
-      </c>
-      <c r="W30">
-        <v>-0.0607843137254902</v>
-      </c>
-      <c r="X30">
-        <v>0.1306718187638068</v>
-      </c>
-      <c r="Y30">
-        <v>-0.191456132489297</v>
-      </c>
-      <c r="Z30">
-        <v>0.05415405314497141</v>
-      </c>
-      <c r="AA30">
-        <v>0</v>
-      </c>
-      <c r="AB30">
-        <v>0.088460190503066</v>
-      </c>
-      <c r="AC30">
-        <v>-0.088460190503066</v>
-      </c>
-      <c r="AD30">
-        <v>20.2</v>
-      </c>
-      <c r="AE30">
-        <v>0</v>
-      </c>
-      <c r="AF30">
-        <v>20.2</v>
-      </c>
-      <c r="AG30">
-        <v>19.799</v>
-      </c>
-      <c r="AH30">
-        <v>0.8244897959183674</v>
-      </c>
-      <c r="AI30">
-        <v>0.9198542805100182</v>
-      </c>
-      <c r="AJ30">
-        <v>0.8215693597244699</v>
-      </c>
-      <c r="AK30">
-        <v>0.918363560461988</v>
-      </c>
-      <c r="AL30">
-        <v>0</v>
-      </c>
-      <c r="AM30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Sri Lanka</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Alliance Finance Company PLC (COSE:ALLI.N0000)</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D31">
-        <v>0.0973</v>
-      </c>
-      <c r="E31">
-        <v>0.0766</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>3.83</v>
-      </c>
-      <c r="L31">
-        <v>0.1595833333333333</v>
-      </c>
-      <c r="M31">
-        <v>0.928</v>
-      </c>
-      <c r="N31">
-        <v>0.05333333333333334</v>
-      </c>
-      <c r="O31">
-        <v>0.2422976501305483</v>
-      </c>
-      <c r="P31">
-        <v>0.928</v>
-      </c>
-      <c r="Q31">
-        <v>0.05333333333333334</v>
-      </c>
-      <c r="R31">
-        <v>0.2422976501305483</v>
-      </c>
-      <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="T31">
-        <v>0</v>
-      </c>
-      <c r="U31">
-        <v>6.45</v>
-      </c>
-      <c r="V31">
-        <v>0.3706896551724138</v>
-      </c>
-      <c r="W31">
-        <v>0.143984962406015</v>
-      </c>
-      <c r="X31">
-        <v>0.1334999323970249</v>
-      </c>
-      <c r="Y31">
-        <v>0.01048503000899015</v>
-      </c>
-      <c r="Z31">
-        <v>0.2262016965127239</v>
-      </c>
-      <c r="AA31">
-        <v>0</v>
-      </c>
-      <c r="AB31">
-        <v>0.08871782816414095</v>
-      </c>
-      <c r="AC31">
-        <v>-0.08871782816414095</v>
-      </c>
-      <c r="AD31">
-        <v>84.3</v>
-      </c>
-      <c r="AE31">
-        <v>0</v>
-      </c>
-      <c r="AF31">
-        <v>84.3</v>
-      </c>
-      <c r="AG31">
-        <v>77.84999999999999</v>
-      </c>
-      <c r="AH31">
-        <v>0.8289085545722714</v>
-      </c>
-      <c r="AI31">
-        <v>0.7336814621409921</v>
-      </c>
-      <c r="AJ31">
-        <v>0.8173228346456692</v>
-      </c>
-      <c r="AK31">
-        <v>0.7178423236514523</v>
-      </c>
-      <c r="AL31">
-        <v>0</v>
-      </c>
-      <c r="AM31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Sri Lanka</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Asia Asset Finance PLC (COSE:AAF.N0000)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D32">
-        <v>0.0863</v>
-      </c>
-      <c r="E32">
-        <v>-0.18</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>0.393</v>
-      </c>
-      <c r="L32">
-        <v>0.06799307958477509</v>
-      </c>
-      <c r="M32">
-        <v>-0</v>
-      </c>
-      <c r="N32">
-        <v>-0</v>
-      </c>
-      <c r="O32">
-        <v>-0</v>
-      </c>
-      <c r="P32">
-        <v>-0</v>
-      </c>
-      <c r="Q32">
-        <v>-0</v>
-      </c>
-      <c r="R32">
-        <v>-0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="U32">
-        <v>7.96</v>
-      </c>
-      <c r="V32">
-        <v>1.54863813229572</v>
-      </c>
-      <c r="W32">
-        <v>0.03358974358974359</v>
-      </c>
-      <c r="X32">
-        <v>0.1626556883346653</v>
-      </c>
-      <c r="Y32">
-        <v>-0.1290659447449217</v>
-      </c>
-      <c r="Z32">
-        <v>0.1465145754119138</v>
-      </c>
-      <c r="AA32">
-        <v>0</v>
-      </c>
-      <c r="AB32">
-        <v>0.09077346512879145</v>
-      </c>
-      <c r="AC32">
-        <v>-0.09077346512879145</v>
-      </c>
-      <c r="AD32">
-        <v>32.7</v>
-      </c>
-      <c r="AE32">
-        <v>0</v>
-      </c>
-      <c r="AF32">
-        <v>32.7</v>
-      </c>
-      <c r="AG32">
-        <v>24.74</v>
-      </c>
-      <c r="AH32">
-        <v>0.8641649048625792</v>
-      </c>
-      <c r="AI32">
-        <v>0.7093275488069415</v>
-      </c>
-      <c r="AJ32">
-        <v>0.8279785809906292</v>
-      </c>
-      <c r="AK32">
-        <v>0.6486628211851075</v>
-      </c>
-      <c r="AL32">
-        <v>0</v>
-      </c>
-      <c r="AM32">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ26"/>
+  <dimension ref="A1:AQ28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,115 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0779</v>
+        <v>0.095</v>
       </c>
       <c r="E2">
-        <v>0.1345</v>
+        <v>0.0762</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.01094860192914955</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.01094860192914955</v>
       </c>
       <c r="I2">
-        <v>3.658448912799784e-05</v>
+        <v>0.00651155197334753</v>
       </c>
       <c r="J2">
-        <v>2.875102206676257e-05</v>
+        <v>0.004948391298203892</v>
       </c>
       <c r="K2">
-        <v>325.092</v>
+        <v>159.652</v>
       </c>
       <c r="L2">
-        <v>0.3861092272993424</v>
+        <v>0.1678799649627913</v>
       </c>
       <c r="M2">
-        <v>16.555</v>
+        <v>20.9348</v>
       </c>
       <c r="N2">
-        <v>0.008986147599713399</v>
+        <v>0.01317018546012733</v>
       </c>
       <c r="O2">
-        <v>0.05092404611617635</v>
+        <v>0.1311277027534888</v>
       </c>
       <c r="P2">
-        <v>16.552</v>
+        <v>20.9348</v>
       </c>
       <c r="Q2">
-        <v>0.008984519182751808</v>
+        <v>0.01317018546012733</v>
       </c>
       <c r="R2">
-        <v>0.05091481795922385</v>
+        <v>0.1311277027534888</v>
       </c>
       <c r="S2">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.0001812141347025068</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>548.355</v>
+        <v>527.741</v>
       </c>
       <c r="V2">
-        <v>0.2976501943244241</v>
+        <v>0.3320044540627595</v>
       </c>
       <c r="W2">
-        <v>0.06832479672929395</v>
+        <v>0.1001990049751244</v>
       </c>
       <c r="X2">
-        <v>0.1371146833235211</v>
+        <v>0.1263151503605373</v>
       </c>
       <c r="Y2">
-        <v>-0.06878988659422719</v>
+        <v>-0.02611614538541294</v>
       </c>
       <c r="Z2">
-        <v>0.1899382278414376</v>
+        <v>0.2716426944472521</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1473444202270199</v>
+        <v>0.1320718744556143</v>
       </c>
       <c r="AC2">
-        <v>-0.1473444202270199</v>
+        <v>-0.1255872401115281</v>
       </c>
       <c r="AD2">
-        <v>2368.402</v>
+        <v>2372.216</v>
       </c>
       <c r="AE2">
-        <v>0.03098497136694392</v>
+        <v>0.02792850209102905</v>
       </c>
       <c r="AF2">
-        <v>2368.432984971367</v>
+        <v>2372.243928502091</v>
       </c>
       <c r="AG2">
-        <v>1820.077984971367</v>
+        <v>1844.502928502091</v>
       </c>
       <c r="AH2">
-        <v>0.5624778970745907</v>
+        <v>0.5987787309300304</v>
       </c>
       <c r="AI2">
-        <v>0.5174617967035562</v>
+        <v>0.4817635042268114</v>
       </c>
       <c r="AJ2">
-        <v>0.4969688906546356</v>
+        <v>0.5371197228778354</v>
       </c>
       <c r="AK2">
-        <v>0.4517819157862546</v>
+        <v>0.4195539243637995</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>2.276</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>2.062</v>
       </c>
       <c r="AN2">
-        <v>64010.86486486487</v>
+        <v>316.5064709806538</v>
+      </c>
+      <c r="AO2">
+        <v>2.708699472759227</v>
       </c>
       <c r="AP2">
-        <v>49191.29689111802</v>
+        <v>246.0977889929408</v>
+      </c>
+      <c r="AQ2">
+        <v>2.989815712900097</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dialog Finance PLC (COSE:CALF.N0000)</t>
+          <t>Lake House Printers and Publishers PLC (COSE:LPRT.N0000)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -715,104 +721,122 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.242</v>
+      </c>
+      <c r="E3">
+        <v>0.532</v>
+      </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.1210884353741496</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.1210884353741496</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.147108843537415</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.09817325287404488</v>
       </c>
       <c r="K3">
-        <v>0.127</v>
+        <v>0.65</v>
       </c>
       <c r="L3">
-        <v>0.1024193548387097</v>
+        <v>0.1105442176870748</v>
       </c>
       <c r="M3">
-        <v>0.003</v>
+        <v>0.018</v>
       </c>
       <c r="N3">
-        <v>0.0001492537313432836</v>
+        <v>0.0119205298013245</v>
       </c>
       <c r="O3">
-        <v>0.02362204724409449</v>
+        <v>0.02769230769230769</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.018</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.0119205298013245</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.02769230769230769</v>
       </c>
       <c r="S3">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>0.226</v>
+        <v>0.85</v>
       </c>
       <c r="V3">
-        <v>0.01124378109452736</v>
+        <v>0.5629139072847682</v>
       </c>
       <c r="W3">
-        <v>0.01</v>
+        <v>0.3110047846889952</v>
       </c>
       <c r="X3">
-        <v>0.08089407829052034</v>
+        <v>0.0933456931534202</v>
       </c>
       <c r="Y3">
-        <v>-0.07089407829052034</v>
+        <v>0.217659091535575</v>
       </c>
       <c r="Z3">
-        <v>0.1893708002443494</v>
+        <v>3.442622950819672</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.3379734935008104</v>
       </c>
       <c r="AB3">
-        <v>0.08105500042662896</v>
+        <v>0.0950153260513513</v>
       </c>
       <c r="AC3">
-        <v>-0.08105500042662896</v>
+        <v>0.2429581674494591</v>
       </c>
       <c r="AD3">
-        <v>0.043</v>
+        <v>0.056</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.043</v>
+        <v>0.056</v>
       </c>
       <c r="AG3">
-        <v>-0.183</v>
+        <v>-0.7939999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.002134736633073524</v>
+        <v>0.03575989782886334</v>
       </c>
       <c r="AI3">
-        <v>0.006028319080330856</v>
+        <v>0.01838476690741957</v>
       </c>
       <c r="AJ3">
-        <v>-0.009188130742581712</v>
+        <v>-1.108938547486033</v>
       </c>
       <c r="AK3">
-        <v>-0.0264948602866657</v>
+        <v>-0.3615664845173041</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-0.07199999999999999</v>
+      </c>
+      <c r="AN3">
+        <v>0.06278026905829596</v>
+      </c>
+      <c r="AO3">
+        <v>18.80434782608696</v>
+      </c>
+      <c r="AP3">
+        <v>-0.890134529147982</v>
+      </c>
+      <c r="AQ3">
+        <v>-12.01388888888889</v>
       </c>
     </row>
     <row r="4">
@@ -823,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LOLC Development Finance PLC (COSE:NIFL.N0000)</t>
+          <t>Printcare PLC (COSE:CARE.N0000)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,106 +856,118 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0723</v>
-      </c>
-      <c r="E4">
-        <v>-0.0701</v>
+        <v>0.231</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.2298578199052132</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.2298578199052132</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.1255924170616114</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.06279620853080568</v>
       </c>
       <c r="K4">
-        <v>0.407</v>
+        <v>0.413</v>
       </c>
       <c r="L4">
-        <v>0.05537414965986395</v>
+        <v>0.009786729857819905</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>1.46</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.1206611570247934</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>3.535108958837772</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>1.46</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.1206611570247934</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>3.535108958837772</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>1.44</v>
+        <v>4.27</v>
       </c>
       <c r="V4">
-        <v>0.002856009520031733</v>
+        <v>0.3528925619834711</v>
       </c>
       <c r="W4">
-        <v>0.02713333333333333</v>
+        <v>0.02533742331288343</v>
       </c>
       <c r="X4">
-        <v>0.08240942547679794</v>
+        <v>0.1315023618796401</v>
       </c>
       <c r="Y4">
-        <v>-0.05527609214346461</v>
+        <v>-0.1061649385667567</v>
       </c>
       <c r="Z4">
-        <v>0.1191441076349489</v>
+        <v>1.532873229204504</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>0.09625862695241554</v>
       </c>
       <c r="AB4">
-        <v>0.08589900019535747</v>
+        <v>0.1357335172865986</v>
       </c>
       <c r="AC4">
-        <v>-0.08589900019535747</v>
+        <v>-0.0394748903341831</v>
       </c>
       <c r="AD4">
-        <v>25</v>
+        <v>11.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>25</v>
+        <v>11.9</v>
       </c>
       <c r="AG4">
-        <v>23.56</v>
+        <v>7.630000000000001</v>
       </c>
       <c r="AH4">
-        <v>0.04724111866969009</v>
+        <v>0.4958333333333333</v>
       </c>
       <c r="AI4">
-        <v>0.6720430107526881</v>
+        <v>0.367283950617284</v>
       </c>
       <c r="AJ4">
-        <v>0.0446415037138093</v>
+        <v>0.3867207298530158</v>
       </c>
       <c r="AK4">
-        <v>0.6588366890380313</v>
+        <v>0.271240668325631</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>2.134</v>
+      </c>
+      <c r="AN4">
+        <v>1.811263318112633</v>
+      </c>
+      <c r="AO4">
+        <v>2.376681614349776</v>
+      </c>
+      <c r="AP4">
+        <v>1.161339421613394</v>
+      </c>
+      <c r="AQ4">
+        <v>2.483598875351453</v>
       </c>
     </row>
     <row r="5">
@@ -951,10 +987,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0294</v>
+        <v>0.00729</v>
       </c>
       <c r="E5">
-        <v>0.113</v>
+        <v>0.0533</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -969,28 +1005,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="L5">
-        <v>0.5113122171945701</v>
+        <v>0.4745417515274949</v>
       </c>
       <c r="M5">
-        <v>2.18</v>
+        <v>2.98</v>
       </c>
       <c r="N5">
-        <v>0.05633074935400516</v>
+        <v>0.04027027027027027</v>
       </c>
       <c r="O5">
-        <v>0.09646017699115045</v>
+        <v>0.1278969957081545</v>
       </c>
       <c r="P5">
-        <v>2.18</v>
+        <v>2.98</v>
       </c>
       <c r="Q5">
-        <v>0.05633074935400516</v>
+        <v>0.04027027027027027</v>
       </c>
       <c r="R5">
-        <v>0.09646017699115045</v>
+        <v>0.1278969957081545</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -999,55 +1035,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>2.84</v>
+        <v>3.13</v>
       </c>
       <c r="V5">
-        <v>0.07338501291989663</v>
+        <v>0.0422972972972973</v>
       </c>
       <c r="W5">
-        <v>0.08705701078582434</v>
+        <v>0.1498392282958199</v>
       </c>
       <c r="X5">
-        <v>0.08335945733977876</v>
+        <v>0.09441120281410229</v>
       </c>
       <c r="Y5">
-        <v>0.003697553446045582</v>
+        <v>0.05542802548171766</v>
       </c>
       <c r="Z5">
-        <v>0.1680480571819633</v>
+        <v>0.3152892827329352</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.08850645057279349</v>
+        <v>0.09713592370552109</v>
       </c>
       <c r="AC5">
-        <v>-0.08850645057279349</v>
+        <v>-0.09713592370552109</v>
       </c>
       <c r="AD5">
-        <v>3.07</v>
+        <v>4.7</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>3.07</v>
+        <v>4.7</v>
       </c>
       <c r="AG5">
-        <v>0.23</v>
+        <v>1.57</v>
       </c>
       <c r="AH5">
-        <v>0.07349772564041177</v>
+        <v>0.05972045743329098</v>
       </c>
       <c r="AI5">
-        <v>0.01878020431883526</v>
+        <v>0.02253116011505273</v>
       </c>
       <c r="AJ5">
-        <v>0.005908040071923966</v>
+        <v>0.02077543998941379</v>
       </c>
       <c r="AK5">
-        <v>0.001431862043204881</v>
+        <v>0.007641018153501729</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1064,7 +1100,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Associated Motor Finance Company PLC (COSE:AMF.N0000)</t>
+          <t>Dialog Finance PLC (COSE:CALF.N0000)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1072,12 +1108,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>-0.0759</v>
-      </c>
-      <c r="E6">
-        <v>-0.0245</v>
-      </c>
       <c r="G6">
         <v>0</v>
       </c>
@@ -1091,10 +1121,10 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>1.07</v>
+        <v>0.17</v>
       </c>
       <c r="L6">
-        <v>0.3364779874213836</v>
+        <v>0.07327586206896552</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1118,55 +1148,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.744</v>
+        <v>0.048</v>
       </c>
       <c r="V6">
-        <v>0.2976</v>
+        <v>0.002487046632124352</v>
       </c>
       <c r="W6">
-        <v>0.09067796610169492</v>
+        <v>0.02397743300423131</v>
       </c>
       <c r="X6">
-        <v>0.08439020585732565</v>
+        <v>0.09515111572240811</v>
       </c>
       <c r="Y6">
-        <v>0.006287760244369264</v>
+        <v>-0.0711736827181768</v>
       </c>
       <c r="Z6">
-        <v>0.2037155669442665</v>
+        <v>0.3358911249457072</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.09131737098725778</v>
+        <v>0.098394067903741</v>
       </c>
       <c r="AC6">
-        <v>-0.09131737098725778</v>
+        <v>-0.098394067903741</v>
       </c>
       <c r="AD6">
-        <v>0.279</v>
+        <v>1.58</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.279</v>
+        <v>1.58</v>
       </c>
       <c r="AG6">
-        <v>-0.465</v>
+        <v>1.532</v>
       </c>
       <c r="AH6">
-        <v>0.1003958258366319</v>
+        <v>0.07567049808429119</v>
       </c>
       <c r="AI6">
-        <v>0.03563673521522545</v>
+        <v>0.1617195496417605</v>
       </c>
       <c r="AJ6">
-        <v>-0.2285012285012285</v>
+        <v>0.07354070660522273</v>
       </c>
       <c r="AK6">
-        <v>-0.06563161609033168</v>
+        <v>0.1575807447027361</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1183,7 +1213,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SMB Finance PLC (COSE:SEMB.N0000)</t>
+          <t>LOLC Finance PLC (COSE:LOFC.N0000)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1192,10 +1222,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.0287</v>
+        <v>0.129</v>
       </c>
       <c r="E7">
-        <v>0.171</v>
+        <v>0.3720000000000001</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1210,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0.107</v>
+        <v>55</v>
       </c>
       <c r="L7">
-        <v>0.200374531835206</v>
+        <v>0.5461767626613704</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1237,55 +1267,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0.417</v>
+        <v>49.3</v>
       </c>
       <c r="V7">
-        <v>0.02512048192771084</v>
+        <v>0.1047821466524973</v>
       </c>
       <c r="W7">
-        <v>0.0066875</v>
+        <v>0.2315789473684211</v>
       </c>
       <c r="X7">
-        <v>0.08979191827278235</v>
+        <v>0.1003854199225617</v>
       </c>
       <c r="Y7">
-        <v>-0.08310441827278235</v>
+        <v>0.1311935274458594</v>
       </c>
       <c r="Z7">
-        <v>0.07072847682119207</v>
+        <v>0.3525910364145659</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.1043647914517388</v>
+        <v>0.1073125841337647</v>
       </c>
       <c r="AC7">
-        <v>-0.1043647914517388</v>
+        <v>-0.1073125841337647</v>
       </c>
       <c r="AD7">
-        <v>4.66</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>4.66</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AG7">
-        <v>4.243</v>
+        <v>50.3</v>
       </c>
       <c r="AH7">
-        <v>0.2191909689557855</v>
+        <v>0.1747061918961585</v>
       </c>
       <c r="AI7">
-        <v>0.3379260333575054</v>
+        <v>0.2321137264041016</v>
       </c>
       <c r="AJ7">
-        <v>0.2035695437317085</v>
+        <v>0.09658218125960062</v>
       </c>
       <c r="AK7">
-        <v>0.3172810887609362</v>
+        <v>0.1324381253291206</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1302,7 +1332,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LOLC Finance PLC (COSE:LOFC.N0000)</t>
+          <t>Associated Motor Finance Company PLC (COSE:AMF.N0000)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1311,10 +1341,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.221</v>
+        <v>0.153</v>
       </c>
       <c r="E8">
-        <v>0.625</v>
+        <v>0.399</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1329,10 +1359,10 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>46.3</v>
+        <v>0.784</v>
       </c>
       <c r="L8">
-        <v>0.6962406015037593</v>
+        <v>0.129159802306425</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1356,55 +1386,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>70.8</v>
+        <v>0.482</v>
       </c>
       <c r="V8">
-        <v>0.1647661158948103</v>
+        <v>0.07862969004893965</v>
       </c>
       <c r="W8">
-        <v>0.2380462724935732</v>
+        <v>0.103841059602649</v>
       </c>
       <c r="X8">
-        <v>0.08966357824958962</v>
+        <v>0.1048733322238125</v>
       </c>
       <c r="Y8">
-        <v>0.1483826942439836</v>
+        <v>-0.001032272621163455</v>
       </c>
       <c r="Z8">
-        <v>0.3490813648293963</v>
+        <v>1.005799502899752</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.1094706721303853</v>
+        <v>0.1129627704980592</v>
       </c>
       <c r="AC8">
-        <v>-0.1094706721303853</v>
+        <v>-0.1129627704980592</v>
       </c>
       <c r="AD8">
-        <v>118.9</v>
+        <v>1.98</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>118.9</v>
+        <v>1.98</v>
       </c>
       <c r="AG8">
-        <v>48.10000000000001</v>
+        <v>1.498</v>
       </c>
       <c r="AH8">
-        <v>0.2167335034633613</v>
+        <v>0.2441430332922318</v>
       </c>
       <c r="AI8">
-        <v>0.3336139169472503</v>
+        <v>0.1733800350262697</v>
       </c>
       <c r="AJ8">
-        <v>0.1006697362913353</v>
+        <v>0.1963817514420556</v>
       </c>
       <c r="AK8">
-        <v>0.1684173669467787</v>
+        <v>0.136953739257634</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1421,7 +1451,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Senkadagala Finance PLC (COSE:SFCL.N0000)</t>
+          <t>SMB Finance PLC (COSE:SEMB.N0000)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1430,10 +1460,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0387</v>
+        <v>0.00631</v>
       </c>
       <c r="E9">
-        <v>0.016</v>
+        <v>0.0998</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1448,85 +1478,82 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>2.66</v>
+        <v>0.357</v>
       </c>
       <c r="L9">
-        <v>0.2797055730809674</v>
+        <v>0.3609706774519717</v>
       </c>
       <c r="M9">
-        <v>0.331</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.003853317811408615</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>0.1244360902255639</v>
+        <v>-0</v>
       </c>
       <c r="P9">
-        <v>0.331</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.003853317811408615</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>0.1244360902255639</v>
+        <v>-0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
-        <v>1.68</v>
+        <v>0.288</v>
       </c>
       <c r="V9">
-        <v>0.01955762514551804</v>
+        <v>0.01932885906040268</v>
       </c>
       <c r="W9">
-        <v>0.08444444444444445</v>
+        <v>0.03923076923076923</v>
       </c>
       <c r="X9">
-        <v>0.1022427373516955</v>
+        <v>0.1065977547898986</v>
       </c>
       <c r="Y9">
-        <v>-0.01779829290725106</v>
+        <v>-0.06736698555912943</v>
       </c>
       <c r="Z9">
-        <v>0.08523032801577343</v>
+        <v>0.07412126208498838</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.1239316483775635</v>
+        <v>0.1155529028089574</v>
       </c>
       <c r="AC9">
-        <v>-0.1239316483775635</v>
+        <v>-0.1155529028089574</v>
       </c>
       <c r="AD9">
-        <v>57.6</v>
+        <v>5.45</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>57.6</v>
+        <v>5.45</v>
       </c>
       <c r="AG9">
-        <v>55.92</v>
+        <v>5.162</v>
       </c>
       <c r="AH9">
-        <v>0.4013937282229965</v>
+        <v>0.2678132678132678</v>
       </c>
       <c r="AI9">
-        <v>0.7328244274809161</v>
+        <v>0.3374613003095976</v>
       </c>
       <c r="AJ9">
-        <v>0.3943026371456776</v>
+        <v>0.2573023626757053</v>
       </c>
       <c r="AK9">
-        <v>0.7269890795631825</v>
+        <v>0.3254318497036944</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1543,7 +1570,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nation Lanka Finance PLC (COSE:CSF.N0000)</t>
+          <t>Senkadagala Finance PLC (COSE:SFCL.N0000)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1552,7 +1579,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.335</v>
+        <v>-0.00029</v>
+      </c>
+      <c r="E10">
+        <v>-0.0818</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1567,82 +1597,85 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>-1.28</v>
+        <v>2.03</v>
       </c>
       <c r="L10">
-        <v>-4.155844155844156</v>
+        <v>0.200990099009901</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>0.147</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.001388101983002833</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>0.07241379310344828</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>0.147</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.001388101983002833</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>0.07241379310344828</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
       <c r="U10">
-        <v>1.14</v>
+        <v>1.77</v>
       </c>
       <c r="V10">
-        <v>0.2857142857142857</v>
+        <v>0.01671388101983003</v>
       </c>
       <c r="W10">
-        <v>-0.3359580052493438</v>
+        <v>0.09666666666666665</v>
       </c>
       <c r="X10">
-        <v>0.1040399735881835</v>
+        <v>0.1071934934756983</v>
       </c>
       <c r="Y10">
-        <v>-0.4399979788375273</v>
+        <v>-0.01052682680903162</v>
       </c>
       <c r="Z10">
-        <v>0.04071919619249074</v>
+        <v>0.1313052522100884</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.1260264223022821</v>
+        <v>0.1156873252011398</v>
       </c>
       <c r="AC10">
-        <v>-0.1260264223022821</v>
+        <v>-0.1156873252011398</v>
       </c>
       <c r="AD10">
-        <v>2.9</v>
+        <v>40.3</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>2.9</v>
+        <v>40.3</v>
       </c>
       <c r="AG10">
-        <v>1.76</v>
+        <v>38.52999999999999</v>
       </c>
       <c r="AH10">
-        <v>0.4208998548621189</v>
+        <v>0.2756497948016416</v>
       </c>
       <c r="AI10">
-        <v>0.773952495329597</v>
+        <v>0.6115326251896812</v>
       </c>
       <c r="AJ10">
-        <v>0.3060869565217391</v>
+        <v>0.2667728311292667</v>
       </c>
       <c r="AK10">
-        <v>0.6751054852320675</v>
+        <v>0.6008108529549352</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1659,7 +1692,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HNB Finance PLC (COSE:HNBF.N0000)</t>
+          <t>People's Merchant Finance PLC (COSE:PMB.N0000)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1667,6 +1700,9 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D11">
+        <v>0.599</v>
+      </c>
       <c r="G11">
         <v>0</v>
       </c>
@@ -1680,10 +1716,10 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>-0.879</v>
+        <v>-0.238</v>
       </c>
       <c r="L11">
-        <v>-0.09052523171987641</v>
+        <v>-0.09224806201550387</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1707,55 +1743,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>1.16</v>
+        <v>3.97</v>
       </c>
       <c r="V11">
-        <v>0.058</v>
+        <v>0.6740237691001698</v>
       </c>
       <c r="W11">
-        <v>-0.03474308300395257</v>
+        <v>-0.03164893617021276</v>
       </c>
       <c r="X11">
-        <v>0.1062177079212713</v>
+        <v>0.1081420636536751</v>
       </c>
       <c r="Y11">
-        <v>-0.1409607909252238</v>
+        <v>-0.1397909998238879</v>
       </c>
       <c r="Z11">
-        <v>0.2823495202093632</v>
+        <v>0.2247386759581882</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.1271096148752578</v>
+        <v>0.1173206677324173</v>
       </c>
       <c r="AC11">
-        <v>-0.1271096148752578</v>
+        <v>-0.1173206677324173</v>
       </c>
       <c r="AD11">
-        <v>15.9</v>
+        <v>2.38</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>15.9</v>
+        <v>2.38</v>
       </c>
       <c r="AG11">
-        <v>14.74</v>
+        <v>-1.59</v>
       </c>
       <c r="AH11">
-        <v>0.4428969359331477</v>
+        <v>0.2877871825876663</v>
       </c>
       <c r="AI11">
-        <v>0.5426621160409556</v>
+        <v>0.2234741784037559</v>
       </c>
       <c r="AJ11">
-        <v>0.4242947610823258</v>
+        <v>-0.3697674418604653</v>
       </c>
       <c r="AK11">
-        <v>0.5238095238095238</v>
+        <v>-0.2380239520958084</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1772,7 +1808,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Softlogic Finance PLC (COSE:CRL.N0000)</t>
+          <t>Abans Finance PLC (COSE:AFSL.N0000)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1781,7 +1817,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.504</v>
+        <v>0.07530000000000001</v>
+      </c>
+      <c r="E12">
+        <v>0.292</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1796,10 +1835,10 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>-4.1</v>
+        <v>0.749</v>
       </c>
       <c r="L12">
-        <v>-32.28346456692913</v>
+        <v>0.1849382716049383</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1808,7 +1847,7 @@
         <v>-0</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P12">
         <v>-0</v>
@@ -1817,61 +1856,61 @@
         <v>-0</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
       <c r="U12">
-        <v>0.786</v>
+        <v>0.798</v>
       </c>
       <c r="V12">
-        <v>0.05171052631578948</v>
+        <v>0.1583333333333334</v>
       </c>
       <c r="W12">
-        <v>-0.1589147286821705</v>
+        <v>0.107</v>
       </c>
       <c r="X12">
-        <v>0.1100336460083249</v>
+        <v>0.1118496187188164</v>
       </c>
       <c r="Y12">
-        <v>-0.2689483746904954</v>
+        <v>-0.004849618718816423</v>
       </c>
       <c r="Z12">
-        <v>0.003311603650586701</v>
+        <v>0.2744646245595012</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.1321222731506645</v>
+        <v>0.1211951644185246</v>
       </c>
       <c r="AC12">
-        <v>-0.1321222731506645</v>
+        <v>-0.1211951644185246</v>
       </c>
       <c r="AD12">
-        <v>13.9</v>
+        <v>2.5</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>13.9</v>
+        <v>2.5</v>
       </c>
       <c r="AG12">
-        <v>13.114</v>
+        <v>1.702</v>
       </c>
       <c r="AH12">
-        <v>0.4776632302405498</v>
+        <v>0.3315649867374005</v>
       </c>
       <c r="AI12">
-        <v>0.5791666666666667</v>
+        <v>0.2127659574468085</v>
       </c>
       <c r="AJ12">
-        <v>0.4631630995267359</v>
+        <v>0.2524473450014832</v>
       </c>
       <c r="AK12">
-        <v>0.5649177220642716</v>
+        <v>0.1554054054054054</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1888,7 +1927,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>People's Merchant Finance PLC (COSE:PMB.N0000)</t>
+          <t>Lanka Credit and Business Finance PLC (COSE:LCBF.N0000)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1909,82 +1948,85 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0.276</v>
+        <v>0.383</v>
       </c>
       <c r="L13">
-        <v>0.1550561797752809</v>
+        <v>0.2139664804469274</v>
       </c>
       <c r="M13">
-        <v>-0</v>
+        <v>0.004</v>
       </c>
       <c r="N13">
-        <v>-0</v>
+        <v>0.0009638554216867469</v>
       </c>
       <c r="O13">
-        <v>-0</v>
+        <v>0.01044386422976501</v>
       </c>
       <c r="P13">
-        <v>-0</v>
+        <v>0.004</v>
       </c>
       <c r="Q13">
-        <v>-0</v>
+        <v>0.0009638554216867469</v>
       </c>
       <c r="R13">
-        <v>-0</v>
+        <v>0.01044386422976501</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
       <c r="U13">
-        <v>1.01</v>
+        <v>0.602</v>
       </c>
       <c r="V13">
-        <v>0.2399049881235154</v>
+        <v>0.1450602409638554</v>
       </c>
       <c r="W13">
-        <v>0.02579439252336449</v>
+        <v>0.05147849462365591</v>
       </c>
       <c r="X13">
-        <v>0.1185311328411344</v>
+        <v>0.1120581884298155</v>
       </c>
       <c r="Y13">
-        <v>-0.09273674031776986</v>
+        <v>-0.06057969380615962</v>
       </c>
       <c r="Z13">
-        <v>0.1375579598145286</v>
+        <v>0.1992209237618253</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.1374028455951991</v>
+        <v>0.1213990230892356</v>
       </c>
       <c r="AC13">
-        <v>-0.1374028455951991</v>
+        <v>-0.1213990230892356</v>
       </c>
       <c r="AD13">
-        <v>4.97</v>
+        <v>2.08</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>4.97</v>
+        <v>2.08</v>
       </c>
       <c r="AG13">
-        <v>3.96</v>
+        <v>1.478</v>
       </c>
       <c r="AH13">
-        <v>0.5413943355119826</v>
+        <v>0.3338683788121991</v>
       </c>
       <c r="AI13">
-        <v>0.3979183346677342</v>
+        <v>0.1911764705882353</v>
       </c>
       <c r="AJ13">
-        <v>0.4847001223990208</v>
+        <v>0.2626154939587776</v>
       </c>
       <c r="AK13">
-        <v>0.3449477351916376</v>
+        <v>0.1438022961665694</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2001,7 +2043,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LB Finance PLC (COSE:LFIN.N0000)</t>
+          <t>HNB Finance PLC (COSE:HNBF.N0000)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2009,12 +2051,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D14">
-        <v>0.132</v>
-      </c>
-      <c r="E14">
-        <v>0.183</v>
-      </c>
       <c r="G14">
         <v>0</v>
       </c>
@@ -2028,85 +2064,82 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>25.1</v>
+        <v>1.39</v>
       </c>
       <c r="L14">
-        <v>0.4190317195325543</v>
+        <v>0.09520547945205479</v>
       </c>
       <c r="M14">
-        <v>7.59</v>
+        <v>-0</v>
       </c>
       <c r="N14">
-        <v>0.1258706467661692</v>
+        <v>-0</v>
       </c>
       <c r="O14">
-        <v>0.302390438247012</v>
+        <v>-0</v>
       </c>
       <c r="P14">
-        <v>7.59</v>
+        <v>-0</v>
       </c>
       <c r="Q14">
-        <v>0.1258706467661692</v>
+        <v>-0</v>
       </c>
       <c r="R14">
-        <v>0.302390438247012</v>
+        <v>-0</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
       <c r="U14">
-        <v>17.5</v>
+        <v>3.24</v>
       </c>
       <c r="V14">
-        <v>0.2902155887230514</v>
+        <v>0.1208955223880597</v>
       </c>
       <c r="W14">
-        <v>0.1704005431093008</v>
+        <v>0.1037313432835821</v>
       </c>
       <c r="X14">
-        <v>0.1315159130187751</v>
+        <v>0.1133635861274566</v>
       </c>
       <c r="Y14">
-        <v>0.03888463009052562</v>
+        <v>-0.009632242843874483</v>
       </c>
       <c r="Z14">
-        <v>0.2885356454720617</v>
+        <v>0.5188343994314143</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.1449340530227302</v>
+        <v>0.1219379351646833</v>
       </c>
       <c r="AC14">
-        <v>-0.1449340530227302</v>
+        <v>-0.1219379351646833</v>
       </c>
       <c r="AD14">
-        <v>95.7</v>
+        <v>14.3</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>95.7</v>
+        <v>14.3</v>
       </c>
       <c r="AG14">
-        <v>78.2</v>
+        <v>11.06</v>
       </c>
       <c r="AH14">
-        <v>0.6134615384615385</v>
+        <v>0.3479318734793188</v>
       </c>
       <c r="AI14">
-        <v>0.5066172578083642</v>
+        <v>0.4642857142857143</v>
       </c>
       <c r="AJ14">
-        <v>0.5646209386281589</v>
+        <v>0.2921288959323825</v>
       </c>
       <c r="AK14">
-        <v>0.456242707117853</v>
+        <v>0.4013062409288824</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2123,7 +2156,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Abans Finance PLC (COSE:AFSL.N0000)</t>
+          <t>LB Finance PLC (COSE:LFIN.N0000)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2132,10 +2165,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.126</v>
+        <v>0.114</v>
       </c>
       <c r="E15">
-        <v>0.29</v>
+        <v>0.133</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2150,82 +2183,85 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>1.1</v>
+        <v>27.5</v>
       </c>
       <c r="L15">
-        <v>0.2702702702702703</v>
+        <v>0.3618421052631579</v>
       </c>
       <c r="M15">
-        <v>-0</v>
+        <v>8.58</v>
       </c>
       <c r="N15">
-        <v>-0</v>
+        <v>0.08041237113402061</v>
       </c>
       <c r="O15">
-        <v>-0</v>
+        <v>0.312</v>
       </c>
       <c r="P15">
-        <v>-0</v>
+        <v>8.58</v>
       </c>
       <c r="Q15">
-        <v>-0</v>
+        <v>0.08041237113402061</v>
       </c>
       <c r="R15">
-        <v>-0</v>
+        <v>0.312</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
       <c r="U15">
-        <v>0.324</v>
+        <v>16.6</v>
       </c>
       <c r="V15">
-        <v>0.07769784172661871</v>
+        <v>0.1555763823805061</v>
       </c>
       <c r="W15">
-        <v>0.1018518518518519</v>
+        <v>0.2960172228202368</v>
       </c>
       <c r="X15">
-        <v>0.1427134536282672</v>
+        <v>0.112708664825319</v>
       </c>
       <c r="Y15">
-        <v>-0.04086160177641529</v>
+        <v>0.1833085579949178</v>
       </c>
       <c r="Z15">
-        <v>0.242204237086408</v>
+        <v>0.4441846873173582</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.1497547874313097</v>
+        <v>0.1220258792092271</v>
       </c>
       <c r="AC15">
-        <v>-0.1497547874313097</v>
+        <v>-0.1220258792092271</v>
       </c>
       <c r="AD15">
-        <v>8.08</v>
+        <v>55.2</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>8.08</v>
+        <v>55.2</v>
       </c>
       <c r="AG15">
-        <v>7.756</v>
+        <v>38.6</v>
       </c>
       <c r="AH15">
-        <v>0.6595918367346939</v>
+        <v>0.3409512044471896</v>
       </c>
       <c r="AI15">
-        <v>0.5358090185676393</v>
+        <v>0.3078639152258784</v>
       </c>
       <c r="AJ15">
-        <v>0.6503437866845547</v>
+        <v>0.2656572608396421</v>
       </c>
       <c r="AK15">
-        <v>0.5256166982922201</v>
+        <v>0.2372464658881377</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2242,7 +2278,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Citizens Development Business Finance PLC (COSE:CDB.N0000)</t>
+          <t>Sarvodaya Development Finance PLC (COSE:SDF.N0000)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2250,12 +2286,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D16">
-        <v>0.209</v>
-      </c>
-      <c r="E16">
-        <v>0.31</v>
-      </c>
       <c r="G16">
         <v>0</v>
       </c>
@@ -2269,28 +2299,28 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>8.720000000000001</v>
+        <v>0.705</v>
       </c>
       <c r="L16">
-        <v>0.3726495726495727</v>
+        <v>0.1563192904656319</v>
       </c>
       <c r="M16">
-        <v>0.717</v>
+        <v>0.463</v>
       </c>
       <c r="N16">
-        <v>0.02219814241486068</v>
+        <v>0.07820945945945947</v>
       </c>
       <c r="O16">
-        <v>0.08222477064220182</v>
+        <v>0.6567375886524823</v>
       </c>
       <c r="P16">
-        <v>0.717</v>
+        <v>0.463</v>
       </c>
       <c r="Q16">
-        <v>0.02219814241486068</v>
+        <v>0.07820945945945947</v>
       </c>
       <c r="R16">
-        <v>0.08222477064220182</v>
+        <v>0.6567375886524823</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2299,55 +2329,55 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>5.94</v>
+        <v>1.44</v>
       </c>
       <c r="V16">
-        <v>0.1839009287925697</v>
+        <v>0.2432432432432432</v>
       </c>
       <c r="W16">
-        <v>0.1156498673740053</v>
+        <v>0.07621621621621621</v>
       </c>
       <c r="X16">
-        <v>0.1569665201873306</v>
+        <v>0.1224297228933005</v>
       </c>
       <c r="Y16">
-        <v>-0.04131665281332526</v>
+        <v>-0.04621350667708425</v>
       </c>
       <c r="Z16">
-        <v>0.1201972467639203</v>
+        <v>0.3216374269005848</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.1544460367999475</v>
+        <v>0.1291486010138291</v>
       </c>
       <c r="AC16">
-        <v>-0.1544460367999475</v>
+        <v>-0.1291486010138291</v>
       </c>
       <c r="AD16">
-        <v>77</v>
+        <v>4.49</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>77</v>
+        <v>4.49</v>
       </c>
       <c r="AG16">
-        <v>71.06</v>
+        <v>3.05</v>
       </c>
       <c r="AH16">
-        <v>0.7044830741079597</v>
+        <v>0.4313160422670509</v>
       </c>
       <c r="AI16">
-        <v>0.6150159744408945</v>
+        <v>0.2917478882391163</v>
       </c>
       <c r="AJ16">
-        <v>0.6875</v>
+        <v>0.3400222965440357</v>
       </c>
       <c r="AK16">
-        <v>0.5958410196209961</v>
+        <v>0.2186379928315412</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2364,7 +2394,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Orient Finance PLC (COSE:BFN.N0000)</t>
+          <t>People's Leasing &amp; Finance PLC (COSE:PLC.N0000)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2373,10 +2403,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.0779</v>
+        <v>0.0156</v>
       </c>
       <c r="E17">
-        <v>0.242</v>
+        <v>-0.0636</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2391,82 +2421,85 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0.747</v>
+        <v>12.1</v>
       </c>
       <c r="L17">
-        <v>0.19453125</v>
+        <v>0.1945337620578778</v>
       </c>
       <c r="M17">
-        <v>-0</v>
+        <v>4.0838</v>
       </c>
       <c r="N17">
-        <v>-0</v>
+        <v>0.0604112426035503</v>
       </c>
       <c r="O17">
-        <v>-0</v>
+        <v>0.337504132231405</v>
       </c>
       <c r="P17">
-        <v>-0</v>
+        <v>4.0838</v>
       </c>
       <c r="Q17">
-        <v>-0</v>
+        <v>0.0604112426035503</v>
       </c>
       <c r="R17">
-        <v>-0</v>
+        <v>0.337504132231405</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
       <c r="U17">
-        <v>0.602</v>
+        <v>16.2</v>
       </c>
       <c r="V17">
-        <v>0.1233606557377049</v>
+        <v>0.2396449704142012</v>
       </c>
       <c r="W17">
-        <v>0.04819354838709677</v>
+        <v>0.104580812445981</v>
       </c>
       <c r="X17">
-        <v>0.1528206819902101</v>
+        <v>0.1302005778277742</v>
       </c>
       <c r="Y17">
-        <v>-0.1046271336031133</v>
+        <v>-0.02561976538179318</v>
       </c>
       <c r="Z17">
-        <v>0.1391808626313882</v>
+        <v>0.3374932175800325</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.1552146789939642</v>
+        <v>0.1349951478973995</v>
       </c>
       <c r="AC17">
-        <v>-0.1552146789939642</v>
+        <v>-0.1349951478973995</v>
       </c>
       <c r="AD17">
-        <v>11</v>
+        <v>64.3</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>11</v>
+        <v>64.3</v>
       </c>
       <c r="AG17">
-        <v>10.398</v>
+        <v>48.09999999999999</v>
       </c>
       <c r="AH17">
-        <v>0.6926952141057935</v>
+        <v>0.4874905231235785</v>
       </c>
       <c r="AI17">
-        <v>0.5453644025780863</v>
+        <v>0.3050284629981024</v>
       </c>
       <c r="AJ17">
-        <v>0.6805864641968844</v>
+        <v>0.4157303370786517</v>
       </c>
       <c r="AK17">
-        <v>0.5313777596075225</v>
+        <v>0.2471736896197328</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2483,7 +2516,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>People's Leasing &amp; Finance PLC (COSE:PLC.N0000)</t>
+          <t>Citizens Development Business Finance PLC (COSE:CDB.N0000)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2492,10 +2525,10 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.066</v>
+        <v>0.095</v>
       </c>
       <c r="E18">
-        <v>0.048</v>
+        <v>-0.0698</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2510,82 +2543,85 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>13.1</v>
+        <v>4.08</v>
       </c>
       <c r="L18">
-        <v>0.229020979020979</v>
+        <v>0.1915492957746479</v>
       </c>
       <c r="M18">
-        <v>-0</v>
+        <v>1.08</v>
       </c>
       <c r="N18">
-        <v>-0</v>
+        <v>0.02741116751269036</v>
       </c>
       <c r="O18">
-        <v>-0</v>
+        <v>0.2647058823529412</v>
       </c>
       <c r="P18">
-        <v>-0</v>
+        <v>1.08</v>
       </c>
       <c r="Q18">
-        <v>-0</v>
+        <v>0.02741116751269036</v>
       </c>
       <c r="R18">
-        <v>-0</v>
+        <v>0.2647058823529412</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
       <c r="U18">
-        <v>17.6</v>
+        <v>9.1</v>
       </c>
       <c r="V18">
-        <v>0.6330935251798562</v>
+        <v>0.2309644670050761</v>
       </c>
       <c r="W18">
-        <v>0.06619504800404244</v>
+        <v>0.08464730290456431</v>
       </c>
       <c r="X18">
-        <v>0.1798613946293333</v>
+        <v>0.1479277246212279</v>
       </c>
       <c r="Y18">
-        <v>-0.1136663466252908</v>
+        <v>-0.06328042171666358</v>
       </c>
       <c r="Z18">
-        <v>0.1591984414138602</v>
+        <v>0.1792446479062879</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.1554194212945281</v>
+        <v>0.1421566330293954</v>
       </c>
       <c r="AC18">
-        <v>-0.1554194212945281</v>
+        <v>-0.1421566330293954</v>
       </c>
       <c r="AD18">
-        <v>86.2</v>
+        <v>54.8</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>86.2</v>
+        <v>54.8</v>
       </c>
       <c r="AG18">
-        <v>68.59999999999999</v>
+        <v>45.7</v>
       </c>
       <c r="AH18">
-        <v>0.756140350877193</v>
+        <v>0.5817409766454353</v>
       </c>
       <c r="AI18">
-        <v>0.4089184060721063</v>
+        <v>0.4853852967227635</v>
       </c>
       <c r="AJ18">
-        <v>0.7116182572614108</v>
+        <v>0.5370152761457109</v>
       </c>
       <c r="AK18">
-        <v>0.3550724637681159</v>
+        <v>0.4402697495183044</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2602,7 +2638,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Merchant Bank of Sri Lanka &amp; Finance PLC (COSE:MBSL.N0000)</t>
+          <t>Orient Finance PLC (COSE:BFN.N0000)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2611,7 +2647,7 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.0375</v>
+        <v>0.05110000000000001</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2626,10 +2662,10 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0.08599999999999999</v>
+        <v>-0.574</v>
       </c>
       <c r="L19">
-        <v>0.01025029797377831</v>
+        <v>-0.178816199376947</v>
       </c>
       <c r="M19">
         <v>-0</v>
@@ -2638,7 +2674,7 @@
         <v>-0</v>
       </c>
       <c r="O19">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P19">
         <v>-0</v>
@@ -2647,61 +2683,61 @@
         <v>-0</v>
       </c>
       <c r="R19">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S19">
         <v>0</v>
       </c>
       <c r="U19">
-        <v>2.01</v>
+        <v>1.12</v>
       </c>
       <c r="V19">
-        <v>0.4144329896907216</v>
+        <v>0.2145593869731801</v>
       </c>
       <c r="W19">
-        <v>0.004257425742574257</v>
+        <v>-0.06259541984732823</v>
       </c>
       <c r="X19">
-        <v>0.1618271332939448</v>
+        <v>0.1482343249637187</v>
       </c>
       <c r="Y19">
-        <v>-0.1575697075513706</v>
+        <v>-0.2108297448110469</v>
       </c>
       <c r="Z19">
-        <v>0.2279891304347826</v>
+        <v>0.1781551781551781</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.155775110019977</v>
+        <v>0.1434540258402002</v>
       </c>
       <c r="AC19">
-        <v>-0.155775110019977</v>
+        <v>-0.1434540258402002</v>
       </c>
       <c r="AD19">
-        <v>12.3</v>
+        <v>7.3</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>12.3</v>
+        <v>7.3</v>
       </c>
       <c r="AG19">
-        <v>10.29</v>
+        <v>6.18</v>
       </c>
       <c r="AH19">
-        <v>0.7172011661807581</v>
+        <v>0.5830670926517572</v>
       </c>
       <c r="AI19">
-        <v>0.4979757085020243</v>
+        <v>0.4055555555555556</v>
       </c>
       <c r="AJ19">
-        <v>0.679656538969617</v>
+        <v>0.5421052631578948</v>
       </c>
       <c r="AK19">
-        <v>0.4535037461436757</v>
+        <v>0.3661137440758294</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2718,7 +2754,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Housing Development Finance Corporation Bank of Sri Lanka (COSE:HDFC.N0000)</t>
+          <t>Softlogic Finance PLC (COSE:CRL.N0000)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2726,104 +2762,80 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D20">
-        <v>0.09810000000000001</v>
-      </c>
-      <c r="E20">
-        <v>0.061</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
       <c r="K20">
-        <v>1.14</v>
-      </c>
-      <c r="L20">
-        <v>0.1302857142857143</v>
+        <v>-10</v>
       </c>
       <c r="M20">
-        <v>0.046</v>
+        <v>-0</v>
       </c>
       <c r="N20">
-        <v>0.009387755102040816</v>
+        <v>-0</v>
       </c>
       <c r="O20">
-        <v>0.04035087719298246</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>0.046</v>
+        <v>-0</v>
       </c>
       <c r="Q20">
-        <v>0.009387755102040816</v>
+        <v>-0</v>
       </c>
       <c r="R20">
-        <v>0.04035087719298246</v>
+        <v>0</v>
       </c>
       <c r="S20">
         <v>0</v>
       </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
       <c r="U20">
-        <v>0.696</v>
+        <v>1.23</v>
       </c>
       <c r="V20">
-        <v>0.1420408163265306</v>
+        <v>0.1108108108108108</v>
       </c>
       <c r="W20">
-        <v>0.03725490196078431</v>
+        <v>-0.9900990099009901</v>
       </c>
       <c r="X20">
-        <v>0.1662152122207784</v>
+        <v>0.1496037372627707</v>
       </c>
       <c r="Y20">
-        <v>-0.128960310259994</v>
+        <v>-1.139702747163761</v>
       </c>
       <c r="Z20">
-        <v>0.1567257746731148</v>
+        <v>0</v>
       </c>
       <c r="AA20">
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.1589822152635667</v>
+        <v>0.1439692762202971</v>
       </c>
       <c r="AC20">
-        <v>-0.1589822152635667</v>
+        <v>-0.1439692762202971</v>
       </c>
       <c r="AD20">
-        <v>13.1</v>
+        <v>15.9</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>13.1</v>
+        <v>15.9</v>
       </c>
       <c r="AG20">
-        <v>12.404</v>
+        <v>14.67</v>
       </c>
       <c r="AH20">
-        <v>0.7277777777777777</v>
+        <v>0.5888888888888889</v>
       </c>
       <c r="AI20">
-        <v>0.4212218649517684</v>
+        <v>0.7957957957957958</v>
       </c>
       <c r="AJ20">
-        <v>0.7168284789644012</v>
+        <v>0.5692665890570431</v>
       </c>
       <c r="AK20">
-        <v>0.4079726351795817</v>
+        <v>0.7824</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -2840,7 +2852,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LOLC Holdings PLC (COSE:LOLC.N0000)</t>
+          <t>Commercial Credit and Finance PLC (COSE:COCR.N0000)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2849,10 +2861,10 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.184</v>
+        <v>0.0168</v>
       </c>
       <c r="E21">
-        <v>0.315</v>
+        <v>0.0071</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2867,82 +2879,85 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>184.1</v>
+        <v>8.08</v>
       </c>
       <c r="L21">
-        <v>0.405595946243666</v>
+        <v>0.2404761904761905</v>
       </c>
       <c r="M21">
-        <v>-0</v>
+        <v>0.838</v>
       </c>
       <c r="N21">
-        <v>-0</v>
+        <v>0.0293006993006993</v>
       </c>
       <c r="O21">
-        <v>-0</v>
+        <v>0.1037128712871287</v>
       </c>
       <c r="P21">
-        <v>-0</v>
+        <v>0.838</v>
       </c>
       <c r="Q21">
-        <v>-0</v>
+        <v>0.0293006993006993</v>
       </c>
       <c r="R21">
-        <v>-0</v>
+        <v>0.1037128712871287</v>
       </c>
       <c r="S21">
         <v>0</v>
       </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
       <c r="U21">
-        <v>405.8</v>
+        <v>6.22</v>
       </c>
       <c r="V21">
-        <v>0.7882672882672883</v>
+        <v>0.2174825174825175</v>
       </c>
       <c r="W21">
-        <v>0.2484480431848853</v>
+        <v>0.1562862669245648</v>
       </c>
       <c r="X21">
-        <v>0.178269977658132</v>
+        <v>0.1590946631501255</v>
       </c>
       <c r="Y21">
-        <v>0.07017806552675332</v>
+        <v>-0.002808396225560755</v>
       </c>
       <c r="Z21">
-        <v>0.2002470551903648</v>
+        <v>0.3149606299212598</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.1617059735501705</v>
+        <v>0.1471797416656277</v>
       </c>
       <c r="AC21">
-        <v>-0.1617059735501705</v>
+        <v>-0.1471797416656277</v>
       </c>
       <c r="AD21">
-        <v>1570.6</v>
+        <v>47.7</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>1570.6</v>
+        <v>47.7</v>
       </c>
       <c r="AG21">
-        <v>1164.8</v>
+        <v>41.48</v>
       </c>
       <c r="AH21">
-        <v>0.7531408842428312</v>
+        <v>0.6251638269986893</v>
       </c>
       <c r="AI21">
-        <v>0.5491032409187847</v>
+        <v>0.4206349206349206</v>
       </c>
       <c r="AJ21">
-        <v>0.6934984520123839</v>
+        <v>0.5918949771689497</v>
       </c>
       <c r="AK21">
-        <v>0.47455693623956</v>
+        <v>0.3870125023325247</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -2959,7 +2974,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Commercial Credit and Finance PLC (COSE:COCR.N0000)</t>
+          <t>Merchant Bank of Sri Lanka &amp; Finance PLC (COSE:MBSL.N0000)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2968,10 +2983,7 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.0449</v>
-      </c>
-      <c r="E22">
-        <v>0.0882</v>
+        <v>0.0297</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -2986,85 +2998,82 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>11.9</v>
+        <v>-0.281</v>
       </c>
       <c r="L22">
-        <v>0.3459302325581395</v>
+        <v>-0.03233601841196779</v>
       </c>
       <c r="M22">
-        <v>2.61</v>
+        <v>-0</v>
       </c>
       <c r="N22">
-        <v>0.1338461538461538</v>
+        <v>-0</v>
       </c>
       <c r="O22">
-        <v>0.2193277310924369</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>2.61</v>
+        <v>-0</v>
       </c>
       <c r="Q22">
-        <v>0.1338461538461538</v>
+        <v>-0</v>
       </c>
       <c r="R22">
-        <v>0.2193277310924369</v>
+        <v>0</v>
       </c>
       <c r="S22">
         <v>0</v>
       </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
       <c r="U22">
-        <v>5.82</v>
+        <v>2.19</v>
       </c>
       <c r="V22">
-        <v>0.2984615384615385</v>
+        <v>0.3067226890756303</v>
       </c>
       <c r="W22">
-        <v>0.1463714637146372</v>
+        <v>-0.02486725663716814</v>
       </c>
       <c r="X22">
-        <v>0.1804116908528859</v>
+        <v>0.1680825935623739</v>
       </c>
       <c r="Y22">
-        <v>-0.03404022713824878</v>
+        <v>-0.192949850199542</v>
       </c>
       <c r="Z22">
-        <v>0.1983852364475202</v>
+        <v>0.4025011579434923</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.1621376581977914</v>
+        <v>0.1497380237135993</v>
       </c>
       <c r="AC22">
-        <v>-0.1621376581977914</v>
+        <v>-0.1497380237135993</v>
       </c>
       <c r="AD22">
-        <v>60.8</v>
+        <v>13.5</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>60.8</v>
+        <v>13.5</v>
       </c>
       <c r="AG22">
-        <v>54.98</v>
+        <v>11.31</v>
       </c>
       <c r="AH22">
-        <v>0.7571606475716065</v>
+        <v>0.6540697674418604</v>
       </c>
       <c r="AI22">
-        <v>0.5404444444444444</v>
+        <v>0.4945054945054945</v>
       </c>
       <c r="AJ22">
-        <v>0.7381847475832439</v>
+        <v>0.6130081300813008</v>
       </c>
       <c r="AK22">
-        <v>0.5153730783652043</v>
+        <v>0.4504181600955795</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3081,7 +3090,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Singer Finance (Lanka) PLC (COSE:SFIN.N0000)</t>
+          <t>Housing Development Finance Corporation Bank of Sri Lanka (COSE:HDFC.N0000)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3090,10 +3099,10 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.146</v>
+        <v>0.133</v>
       </c>
       <c r="E23">
-        <v>0.0864</v>
+        <v>0.163</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3102,103 +3111,94 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>0.003615376258991926</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>0.002317127511444825</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>1.55</v>
+        <v>4.33</v>
       </c>
       <c r="L23">
-        <v>0.181924882629108</v>
+        <v>0.2740506329113924</v>
       </c>
       <c r="M23">
-        <v>0.438</v>
+        <v>-0</v>
       </c>
       <c r="N23">
-        <v>0.08036697247706422</v>
+        <v>-0</v>
       </c>
       <c r="O23">
-        <v>0.2825806451612903</v>
+        <v>-0</v>
       </c>
       <c r="P23">
-        <v>0.438</v>
+        <v>-0</v>
       </c>
       <c r="Q23">
-        <v>0.08036697247706422</v>
+        <v>-0</v>
       </c>
       <c r="R23">
-        <v>0.2825806451612903</v>
+        <v>-0</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
       <c r="U23">
-        <v>1.28</v>
+        <v>0.713</v>
       </c>
       <c r="V23">
-        <v>0.2348623853211009</v>
+        <v>0.1128164556962025</v>
       </c>
       <c r="W23">
-        <v>0.07045454545454545</v>
+        <v>0.2405555555555556</v>
       </c>
       <c r="X23">
-        <v>0.249788916745079</v>
+        <v>0.1798873188994812</v>
       </c>
       <c r="Y23">
-        <v>-0.1793343712905336</v>
+        <v>0.06066823665607432</v>
       </c>
       <c r="Z23">
-        <v>0.1250715914278277</v>
+        <v>0.5196684646757006</v>
       </c>
       <c r="AA23">
-        <v>0.0002898068253976064</v>
+        <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.1637928205547931</v>
+        <v>0.1525537615418888</v>
       </c>
       <c r="AC23">
-        <v>-0.1635030137293955</v>
+        <v>-0.1525537615418888</v>
       </c>
       <c r="AD23">
-        <v>28.8</v>
+        <v>13.8</v>
       </c>
       <c r="AE23">
-        <v>0.03098497136694392</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>28.83098497136695</v>
+        <v>13.8</v>
       </c>
       <c r="AG23">
-        <v>27.55098497136694</v>
+        <v>13.087</v>
       </c>
       <c r="AH23">
-        <v>0.8410197371938964</v>
+        <v>0.6858846918489065</v>
       </c>
       <c r="AI23">
-        <v>0.6892255822114057</v>
+        <v>0.3575129533678756</v>
       </c>
       <c r="AJ23">
-        <v>0.8348534140805599</v>
+        <v>0.6743443087545731</v>
       </c>
       <c r="AK23">
-        <v>0.6794159251821059</v>
+        <v>0.3454219125293637</v>
       </c>
       <c r="AL23">
         <v>0</v>
       </c>
       <c r="AM23">
         <v>0</v>
-      </c>
-      <c r="AN23">
-        <v>778.3783783783784</v>
-      </c>
-      <c r="AP23">
-        <v>744.6212154423499</v>
       </c>
     </row>
     <row r="24">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vallibel Finance PLC (COSE:VFIN.N0000)</t>
+          <t>Singer Finance (Lanka) PLC (COSE:SFIN.N0000)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="D24">
-        <v>0.168</v>
+        <v>0.103</v>
       </c>
       <c r="E24">
-        <v>0.209</v>
+        <v>-0.0306</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3230,34 +3230,34 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>0.002714287087306356</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>0.001641783384224685</v>
       </c>
       <c r="K24">
-        <v>5.91</v>
+        <v>1.37</v>
       </c>
       <c r="L24">
-        <v>0.3993243243243243</v>
+        <v>0.1356435643564357</v>
       </c>
       <c r="M24">
-        <v>1.29</v>
+        <v>0.002</v>
       </c>
       <c r="N24">
-        <v>0.08958333333333333</v>
+        <v>0.00028328611898017</v>
       </c>
       <c r="O24">
-        <v>0.2182741116751269</v>
+        <v>0.00145985401459854</v>
       </c>
       <c r="P24">
-        <v>1.29</v>
+        <v>0.002</v>
       </c>
       <c r="Q24">
-        <v>0.08958333333333333</v>
+        <v>0.00028328611898017</v>
       </c>
       <c r="R24">
-        <v>0.2182741116751269</v>
+        <v>0.00145985401459854</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -3266,61 +3266,67 @@
         <v>0</v>
       </c>
       <c r="U24">
-        <v>3.04</v>
+        <v>4.82</v>
       </c>
       <c r="V24">
-        <v>0.2111111111111111</v>
+        <v>0.6827195467422097</v>
       </c>
       <c r="W24">
-        <v>0.1293216630196936</v>
+        <v>0.1053846153846154</v>
       </c>
       <c r="X24">
-        <v>0.2265500374880186</v>
+        <v>0.1993732152964913</v>
       </c>
       <c r="Y24">
-        <v>-0.09722837446832497</v>
+        <v>-0.09398859991187587</v>
       </c>
       <c r="Z24">
-        <v>0.1138461538461538</v>
+        <v>0.249087940447541</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>0.0004089484418375207</v>
       </c>
       <c r="AB24">
-        <v>0.168910144354098</v>
+        <v>0.1547426753594532</v>
       </c>
       <c r="AC24">
-        <v>-0.168910144354098</v>
+        <v>-0.1543337269176157</v>
       </c>
       <c r="AD24">
-        <v>65.7</v>
+        <v>18.8</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>0.02792850209102905</v>
       </c>
       <c r="AF24">
-        <v>65.7</v>
+        <v>18.82792850209103</v>
       </c>
       <c r="AG24">
-        <v>62.66</v>
+        <v>14.00792850209103</v>
       </c>
       <c r="AH24">
-        <v>0.8202247191011235</v>
+        <v>0.7272860206088043</v>
       </c>
       <c r="AI24">
-        <v>0.698936170212766</v>
+        <v>0.5390508200611971</v>
       </c>
       <c r="AJ24">
-        <v>0.8131326239294057</v>
+        <v>0.6648934896803318</v>
       </c>
       <c r="AK24">
-        <v>0.6888742304309586</v>
+        <v>0.4652571332205124</v>
       </c>
       <c r="AL24">
         <v>0</v>
       </c>
       <c r="AM24">
         <v>0</v>
+      </c>
+      <c r="AN24">
+        <v>569.6969696969697</v>
+      </c>
+      <c r="AP24">
+        <v>424.4826818815463</v>
       </c>
     </row>
     <row r="25">
@@ -3331,7 +3337,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Alliance Finance Company PLC (COSE:ALLI.N0000)</t>
+          <t>Vallibel Finance PLC (COSE:VFIN.N0000)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3340,10 +3346,10 @@
         </is>
       </c>
       <c r="D25">
-        <v>0.138</v>
+        <v>0.152</v>
       </c>
       <c r="E25">
-        <v>0.156</v>
+        <v>0.0762</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3358,28 +3364,28 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>3.71</v>
+        <v>4.94</v>
       </c>
       <c r="L25">
-        <v>0.2348101265822785</v>
+        <v>0.2409756097560976</v>
       </c>
       <c r="M25">
-        <v>1.35</v>
+        <v>0.729</v>
       </c>
       <c r="N25">
-        <v>0.2581261950286807</v>
+        <v>0.03128755364806867</v>
       </c>
       <c r="O25">
-        <v>0.3638814016172507</v>
+        <v>0.1475708502024291</v>
       </c>
       <c r="P25">
-        <v>1.35</v>
+        <v>0.729</v>
       </c>
       <c r="Q25">
-        <v>0.2581261950286807</v>
+        <v>0.03128755364806867</v>
       </c>
       <c r="R25">
-        <v>0.3638814016172507</v>
+        <v>0.1475708502024291</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -3388,55 +3394,55 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>1.91</v>
+        <v>6.32</v>
       </c>
       <c r="V25">
-        <v>0.3652007648183556</v>
+        <v>0.2712446351931331</v>
       </c>
       <c r="W25">
-        <v>0.1224422442244224</v>
+        <v>0.1745583038869258</v>
       </c>
       <c r="X25">
-        <v>0.4912156345071501</v>
+        <v>0.2069220923973415</v>
       </c>
       <c r="Y25">
-        <v>-0.3687733902827276</v>
+        <v>-0.03236378851041569</v>
       </c>
       <c r="Z25">
-        <v>0.1460933888118354</v>
+        <v>0.2253737906772208</v>
       </c>
       <c r="AA25">
         <v>0</v>
       </c>
       <c r="AB25">
-        <v>0.1777824286357459</v>
+        <v>0.1573904724429356</v>
       </c>
       <c r="AC25">
-        <v>-0.1777824286357459</v>
+        <v>-0.1573904724429356</v>
       </c>
       <c r="AD25">
-        <v>67.2</v>
+        <v>66.5</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>67.2</v>
+        <v>66.5</v>
       </c>
       <c r="AG25">
-        <v>65.29000000000001</v>
+        <v>60.18</v>
       </c>
       <c r="AH25">
-        <v>0.9277923512356758</v>
+        <v>0.7405345211581292</v>
       </c>
       <c r="AI25">
-        <v>0.7823050058207217</v>
+        <v>0.646887159533074</v>
       </c>
       <c r="AJ25">
-        <v>0.9258366420873511</v>
+        <v>0.7208912314326784</v>
       </c>
       <c r="AK25">
-        <v>0.7773544469579712</v>
+        <v>0.6237562189054727</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -3453,114 +3459,355 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>LOLC Holdings PLC (COSE:LOLC.N0000)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>0.08359999999999999</v>
+      </c>
+      <c r="E26">
+        <v>-0.07290000000000001</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>19.9</v>
+      </c>
+      <c r="L26">
+        <v>0.04575764543573235</v>
+      </c>
+      <c r="M26">
+        <v>-0</v>
+      </c>
+      <c r="N26">
+        <v>-0</v>
+      </c>
+      <c r="O26">
+        <v>-0</v>
+      </c>
+      <c r="P26">
+        <v>-0</v>
+      </c>
+      <c r="Q26">
+        <v>-0</v>
+      </c>
+      <c r="R26">
+        <v>-0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>380.7</v>
+      </c>
+      <c r="V26">
+        <v>0.7293103448275862</v>
+      </c>
+      <c r="W26">
+        <v>0.02596216568819308</v>
+      </c>
+      <c r="X26">
+        <v>0.2252408040791616</v>
+      </c>
+      <c r="Y26">
+        <v>-0.1992786383909685</v>
+      </c>
+      <c r="Z26">
+        <v>0.2251851084761559</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0.1582545058984797</v>
+      </c>
+      <c r="AC26">
+        <v>-0.1582545058984797</v>
+      </c>
+      <c r="AD26">
+        <v>1727</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>1727</v>
+      </c>
+      <c r="AG26">
+        <v>1346.3</v>
+      </c>
+      <c r="AH26">
+        <v>0.7678968430413518</v>
+      </c>
+      <c r="AI26">
+        <v>0.5603686037833804</v>
+      </c>
+      <c r="AJ26">
+        <v>0.7206016164427554</v>
+      </c>
+      <c r="AK26">
+        <v>0.498408114911891</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>Asia Asset Finance PLC (COSE:AAF.N0000)</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D26">
-        <v>0.105</v>
-      </c>
-      <c r="E26">
-        <v>-0.0217</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0.641</v>
-      </c>
-      <c r="L26">
-        <v>0.1405701754385965</v>
-      </c>
-      <c r="M26">
-        <v>-0</v>
-      </c>
-      <c r="N26">
-        <v>-0</v>
-      </c>
-      <c r="O26">
-        <v>-0</v>
-      </c>
-      <c r="P26">
-        <v>-0</v>
-      </c>
-      <c r="Q26">
-        <v>-0</v>
-      </c>
-      <c r="R26">
-        <v>-0</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="U26">
-        <v>3.59</v>
-      </c>
-      <c r="V26">
-        <v>1.380769230769231</v>
-      </c>
-      <c r="W26">
-        <v>0.04783582089552239</v>
-      </c>
-      <c r="X26">
-        <v>0.3842516638279827</v>
-      </c>
-      <c r="Y26">
-        <v>-0.3364158429324603</v>
-      </c>
-      <c r="Z26">
-        <v>0.1195595175668589</v>
-      </c>
-      <c r="AA26">
-        <v>0</v>
-      </c>
-      <c r="AB26">
-        <v>0.17798864032962</v>
-      </c>
-      <c r="AC26">
-        <v>-0.17798864032962</v>
-      </c>
-      <c r="AD26">
-        <v>24.7</v>
-      </c>
-      <c r="AE26">
-        <v>0</v>
-      </c>
-      <c r="AF26">
-        <v>24.7</v>
-      </c>
-      <c r="AG26">
-        <v>21.11</v>
-      </c>
-      <c r="AH26">
-        <v>0.9047619047619048</v>
-      </c>
-      <c r="AI26">
-        <v>0.758133824432167</v>
-      </c>
-      <c r="AJ26">
-        <v>0.8903416280050611</v>
-      </c>
-      <c r="AK26">
-        <v>0.7281821317695757</v>
-      </c>
-      <c r="AL26">
-        <v>0</v>
-      </c>
-      <c r="AM26">
+      <c r="D27">
+        <v>0.13</v>
+      </c>
+      <c r="E27">
+        <v>0.179</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0.844</v>
+      </c>
+      <c r="L27">
+        <v>0.1534545454545455</v>
+      </c>
+      <c r="M27">
+        <v>-0</v>
+      </c>
+      <c r="N27">
+        <v>-0</v>
+      </c>
+      <c r="O27">
+        <v>-0</v>
+      </c>
+      <c r="P27">
+        <v>-0</v>
+      </c>
+      <c r="Q27">
+        <v>-0</v>
+      </c>
+      <c r="R27">
+        <v>-0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>8.58</v>
+      </c>
+      <c r="V27">
+        <v>1.849137931034483</v>
+      </c>
+      <c r="W27">
+        <v>0.1071065989847716</v>
+      </c>
+      <c r="X27">
+        <v>0.3195100194857796</v>
+      </c>
+      <c r="Y27">
+        <v>-0.212403420501008</v>
+      </c>
+      <c r="Z27">
+        <v>0.1897205933080373</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0.1670383931777363</v>
+      </c>
+      <c r="AC27">
+        <v>-0.1670383931777363</v>
+      </c>
+      <c r="AD27">
+        <v>26.2</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>26.2</v>
+      </c>
+      <c r="AG27">
+        <v>17.62</v>
+      </c>
+      <c r="AH27">
+        <v>0.8495460440985733</v>
+      </c>
+      <c r="AI27">
+        <v>0.7293986636971046</v>
+      </c>
+      <c r="AJ27">
+        <v>0.7915543575920934</v>
+      </c>
+      <c r="AK27">
+        <v>0.6444769568397951</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Alliance Finance Company PLC (COSE:ALLI.N0000)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>0.0833</v>
+      </c>
+      <c r="E28">
+        <v>-0.0173</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>1.67</v>
+      </c>
+      <c r="L28">
+        <v>0.1167832167832168</v>
+      </c>
+      <c r="M28">
+        <v>0.55</v>
+      </c>
+      <c r="N28">
+        <v>0.06594724220623502</v>
+      </c>
+      <c r="O28">
+        <v>0.3293413173652695</v>
+      </c>
+      <c r="P28">
+        <v>0.55</v>
+      </c>
+      <c r="Q28">
+        <v>0.06594724220623502</v>
+      </c>
+      <c r="R28">
+        <v>0.3293413173652695</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>3.76</v>
+      </c>
+      <c r="V28">
+        <v>0.4508393285371702</v>
+      </c>
+      <c r="W28">
+        <v>0.09027027027027026</v>
+      </c>
+      <c r="X28">
+        <v>0.429770319339871</v>
+      </c>
+      <c r="Y28">
+        <v>-0.3395000490696007</v>
+      </c>
+      <c r="Z28">
+        <v>0.1706647571309226</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0.1709200639478419</v>
+      </c>
+      <c r="AC28">
+        <v>-0.1709200639478419</v>
+      </c>
+      <c r="AD28">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AG28">
+        <v>66.14</v>
+      </c>
+      <c r="AH28">
+        <v>0.8934049079754601</v>
+      </c>
+      <c r="AI28">
+        <v>0.7564935064935066</v>
+      </c>
+      <c r="AJ28">
+        <v>0.8880236305048335</v>
+      </c>
+      <c r="AK28">
+        <v>0.7461642599277979</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
         <v>0</v>
       </c>
     </row>
